--- a/research/traditional_assets/database/data/romania/romania_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_healthcare_support_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1056627252267189</v>
+        <v>0.1055314648663562</v>
       </c>
       <c r="C2">
-        <v>1058.913710956921</v>
+        <v>1050.967428582707</v>
       </c>
       <c r="D2">
-        <v>1024.213710956921</v>
+        <v>1026.464428582707</v>
       </c>
       <c r="E2">
-        <v>-378.6</v>
+        <v>-368.403</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.197</v>
       </c>
       <c r="G2">
         <v>34.7</v>
@@ -1451,28 +1451,28 @@
         <v>53.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5129091</v>
       </c>
       <c r="N2">
-        <v>53.8</v>
+        <v>53.2870909</v>
       </c>
       <c r="O2">
-        <v>8.608000000000001</v>
+        <v>8.525934544</v>
       </c>
       <c r="P2">
-        <v>45.19199999999999</v>
+        <v>44.76115635599999</v>
       </c>
       <c r="Q2">
-        <v>96.892</v>
+        <v>96.461156356</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1056627252267189</v>
+        <v>0.1061706513801577</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738455</v>
+        <v>0.8310247400618661</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>104.8918804521113</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1055314648663562</v>
+        <v>0.1054002045059934</v>
       </c>
       <c r="C3">
-        <v>1050.967428582707</v>
+        <v>1043.031059933087</v>
       </c>
       <c r="D3">
-        <v>1026.464428582707</v>
+        <v>1028.725059933087</v>
       </c>
       <c r="E3">
-        <v>-368.403</v>
+        <v>-358.206</v>
       </c>
       <c r="F3">
-        <v>10.197</v>
+        <v>20.394</v>
       </c>
       <c r="G3">
         <v>34.7</v>
@@ -1533,28 +1533,28 @@
         <v>53.8</v>
       </c>
       <c r="M3">
-        <v>0.5129091</v>
+        <v>1.0258182</v>
       </c>
       <c r="N3">
-        <v>53.2870909</v>
+        <v>52.77418179999999</v>
       </c>
       <c r="O3">
-        <v>8.525934544</v>
+        <v>8.443869088</v>
       </c>
       <c r="P3">
-        <v>44.76115635599999</v>
+        <v>44.33031271199999</v>
       </c>
       <c r="Q3">
-        <v>96.461156356</v>
+        <v>96.030312712</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1061706513801577</v>
+        <v>0.1066889433734627</v>
       </c>
       <c r="T3">
-        <v>0.8310247400618661</v>
+        <v>0.8381592244373971</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>104.8918804521113</v>
+        <v>52.44594022605564</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1054002045059934</v>
+        <v>0.1052689441456307</v>
       </c>
       <c r="C4">
-        <v>1043.031059933087</v>
+        <v>1035.104670653034</v>
       </c>
       <c r="D4">
-        <v>1028.725059933087</v>
+        <v>1030.995670653034</v>
       </c>
       <c r="E4">
-        <v>-358.206</v>
+        <v>-348.009</v>
       </c>
       <c r="F4">
-        <v>20.394</v>
+        <v>30.591</v>
       </c>
       <c r="G4">
         <v>34.7</v>
@@ -1615,28 +1615,28 @@
         <v>53.8</v>
       </c>
       <c r="M4">
-        <v>1.0258182</v>
+        <v>1.5387273</v>
       </c>
       <c r="N4">
-        <v>52.77418179999999</v>
+        <v>52.2612727</v>
       </c>
       <c r="O4">
-        <v>8.443869088</v>
+        <v>8.361803632000001</v>
       </c>
       <c r="P4">
-        <v>44.33031271199999</v>
+        <v>43.899469068</v>
       </c>
       <c r="Q4">
-        <v>96.030312712</v>
+        <v>95.599469068</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1066889433734627</v>
+        <v>0.1072179217996192</v>
       </c>
       <c r="T4">
-        <v>0.8381592244373971</v>
+        <v>0.8454408115835578</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>52.44594022605564</v>
+        <v>34.96396015070377</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1052689441456307</v>
+        <v>0.1051376837852679</v>
       </c>
       <c r="C5">
-        <v>1035.104670653034</v>
+        <v>1027.188326968371</v>
       </c>
       <c r="D5">
-        <v>1030.995670653034</v>
+        <v>1033.276326968371</v>
       </c>
       <c r="E5">
-        <v>-348.009</v>
+        <v>-337.812</v>
       </c>
       <c r="F5">
-        <v>30.591</v>
+        <v>40.788</v>
       </c>
       <c r="G5">
         <v>34.7</v>
@@ -1697,28 +1697,28 @@
         <v>53.8</v>
       </c>
       <c r="M5">
-        <v>1.5387273</v>
+        <v>2.0516364</v>
       </c>
       <c r="N5">
-        <v>52.2612727</v>
+        <v>51.7483636</v>
       </c>
       <c r="O5">
-        <v>8.361803632000001</v>
+        <v>8.279738176</v>
       </c>
       <c r="P5">
-        <v>43.899469068</v>
+        <v>43.468625424</v>
       </c>
       <c r="Q5">
-        <v>95.599469068</v>
+        <v>95.168625424</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1072179217996192</v>
+        <v>0.1077579206096541</v>
       </c>
       <c r="T5">
-        <v>0.8454408115835578</v>
+        <v>0.8528740984619301</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.96396015070377</v>
+        <v>26.22297011302782</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1051376837852679</v>
+        <v>0.1050064234249052</v>
       </c>
       <c r="C6">
-        <v>1027.188326968371</v>
+        <v>1019.282095692211</v>
       </c>
       <c r="D6">
-        <v>1033.276326968371</v>
+        <v>1035.567095692211</v>
       </c>
       <c r="E6">
-        <v>-337.812</v>
+        <v>-327.615</v>
       </c>
       <c r="F6">
-        <v>40.788</v>
+        <v>50.98500000000001</v>
       </c>
       <c r="G6">
         <v>34.7</v>
@@ -1779,28 +1779,28 @@
         <v>53.8</v>
       </c>
       <c r="M6">
-        <v>2.0516364</v>
+        <v>2.5645455</v>
       </c>
       <c r="N6">
-        <v>51.7483636</v>
+        <v>51.2354545</v>
       </c>
       <c r="O6">
-        <v>8.279738176</v>
+        <v>8.19767272</v>
       </c>
       <c r="P6">
-        <v>43.468625424</v>
+        <v>43.03778178</v>
       </c>
       <c r="Q6">
-        <v>95.168625424</v>
+        <v>94.73778178000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1077579206096541</v>
+        <v>0.1083092878156896</v>
       </c>
       <c r="T6">
-        <v>0.8528740984619301</v>
+        <v>0.8604638755903734</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.22297011302782</v>
+        <v>20.97837609042226</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1050064234249052</v>
+        <v>0.1048751630645424</v>
       </c>
       <c r="C7">
-        <v>1019.282095692211</v>
+        <v>1011.386044231478</v>
       </c>
       <c r="D7">
-        <v>1035.567095692211</v>
+        <v>1037.868044231478</v>
       </c>
       <c r="E7">
-        <v>-327.615</v>
+        <v>-317.418</v>
       </c>
       <c r="F7">
-        <v>50.98500000000001</v>
+        <v>61.18200000000001</v>
       </c>
       <c r="G7">
         <v>34.7</v>
@@ -1861,28 +1861,28 @@
         <v>53.8</v>
       </c>
       <c r="M7">
-        <v>2.5645455</v>
+        <v>3.0774546</v>
       </c>
       <c r="N7">
-        <v>51.2354545</v>
+        <v>50.72254539999999</v>
       </c>
       <c r="O7">
-        <v>8.19767272</v>
+        <v>8.115607263999999</v>
       </c>
       <c r="P7">
-        <v>43.03778178</v>
+        <v>42.606938136</v>
       </c>
       <c r="Q7">
-        <v>94.73778178000001</v>
+        <v>94.306938136</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1083092878156896</v>
+        <v>0.1088723862388749</v>
       </c>
       <c r="T7">
-        <v>0.8604638755903734</v>
+        <v>0.8682151373385709</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.97837609042226</v>
+        <v>17.48198007535188</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1048751630645424</v>
+        <v>0.1047439027041797</v>
       </c>
       <c r="C8">
-        <v>1011.386044231478</v>
+        <v>1003.500240593526</v>
       </c>
       <c r="D8">
-        <v>1037.868044231478</v>
+        <v>1040.179240593526</v>
       </c>
       <c r="E8">
-        <v>-317.418</v>
+        <v>-307.221</v>
       </c>
       <c r="F8">
-        <v>61.182</v>
+        <v>71.37899999999999</v>
       </c>
       <c r="G8">
         <v>34.7</v>
@@ -1943,28 +1943,28 @@
         <v>53.8</v>
       </c>
       <c r="M8">
-        <v>3.0774546</v>
+        <v>3.590363699999999</v>
       </c>
       <c r="N8">
-        <v>50.72254539999999</v>
+        <v>50.2096363</v>
       </c>
       <c r="O8">
-        <v>8.115607263999999</v>
+        <v>8.033541808000001</v>
       </c>
       <c r="P8">
-        <v>42.606938136</v>
+        <v>42.176094492</v>
       </c>
       <c r="Q8">
-        <v>94.306938136</v>
+        <v>93.87609449199999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1088723862388749</v>
+        <v>0.1094475943055695</v>
       </c>
       <c r="T8">
-        <v>0.8682151373385709</v>
+        <v>0.8761330928878048</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.48198007535188</v>
+        <v>14.98455435030162</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1047439027041796</v>
+        <v>0.1046126423438169</v>
       </c>
       <c r="C9">
-        <v>1003.500240593527</v>
+        <v>995.6247533928322</v>
       </c>
       <c r="D9">
-        <v>1040.179240593527</v>
+        <v>1042.500753392832</v>
       </c>
       <c r="E9">
-        <v>-307.221</v>
+        <v>-297.024</v>
       </c>
       <c r="F9">
-        <v>71.379</v>
+        <v>81.57600000000001</v>
       </c>
       <c r="G9">
         <v>34.7</v>
@@ -2025,28 +2025,28 @@
         <v>53.8</v>
       </c>
       <c r="M9">
-        <v>3.5903637</v>
+        <v>4.1032728</v>
       </c>
       <c r="N9">
-        <v>50.2096363</v>
+        <v>49.6967272</v>
       </c>
       <c r="O9">
-        <v>8.033541808000001</v>
+        <v>7.951476352</v>
       </c>
       <c r="P9">
-        <v>42.176094492</v>
+        <v>41.745250848</v>
       </c>
       <c r="Q9">
-        <v>93.87609449199999</v>
+        <v>93.445250848</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1094475943055695</v>
+        <v>0.1100353068954532</v>
       </c>
       <c r="T9">
-        <v>0.8761330928878048</v>
+        <v>0.8842231779055003</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.98455435030161</v>
+        <v>13.11148505651391</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1046126423438169</v>
+        <v>0.1045947819834542</v>
       </c>
       <c r="C10">
-        <v>995.6247533928322</v>
+        <v>985.7444386241722</v>
       </c>
       <c r="D10">
-        <v>1042.500753392832</v>
+        <v>1042.817438624172</v>
       </c>
       <c r="E10">
-        <v>-297.024</v>
+        <v>-286.827</v>
       </c>
       <c r="F10">
-        <v>81.57600000000001</v>
+        <v>91.773</v>
       </c>
       <c r="G10">
         <v>34.7</v>
@@ -2107,45 +2107,45 @@
         <v>53.8</v>
       </c>
       <c r="M10">
-        <v>4.1032728</v>
+        <v>4.7538414</v>
       </c>
       <c r="N10">
-        <v>49.6967272</v>
+        <v>49.0461586</v>
       </c>
       <c r="O10">
-        <v>7.951476352</v>
+        <v>7.847385376</v>
       </c>
       <c r="P10">
-        <v>41.745250848</v>
+        <v>41.198773224</v>
       </c>
       <c r="Q10">
-        <v>93.445250848</v>
+        <v>92.898773224</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1100353068954532</v>
+        <v>0.110635936245554</v>
       </c>
       <c r="T10">
-        <v>0.8842231779055003</v>
+        <v>0.8924910669895189</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.16</v>
       </c>
       <c r="W10">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.11148505651391</v>
+        <v>11.31716342072329</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1045947819834542</v>
+        <v>0.1044761216230914</v>
       </c>
       <c r="C11">
-        <v>985.7444386241722</v>
+        <v>977.6563219251948</v>
       </c>
       <c r="D11">
-        <v>1042.817438624172</v>
+        <v>1044.926321925195</v>
       </c>
       <c r="E11">
-        <v>-286.827</v>
+        <v>-276.63</v>
       </c>
       <c r="F11">
-        <v>91.773</v>
+        <v>101.97</v>
       </c>
       <c r="G11">
         <v>34.7</v>
@@ -2189,28 +2189,28 @@
         <v>53.8</v>
       </c>
       <c r="M11">
-        <v>4.7538414</v>
+        <v>5.282046</v>
       </c>
       <c r="N11">
-        <v>49.0461586</v>
+        <v>48.517954</v>
       </c>
       <c r="O11">
-        <v>7.847385376</v>
+        <v>7.762872639999999</v>
       </c>
       <c r="P11">
-        <v>41.198773224</v>
+        <v>40.75508136</v>
       </c>
       <c r="Q11">
-        <v>92.898773224</v>
+        <v>92.45508136000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.110635936245554</v>
+        <v>0.111249912914546</v>
       </c>
       <c r="T11">
-        <v>0.8924910669895189</v>
+        <v>0.900942686942071</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.31716342072329</v>
+        <v>10.18544707865096</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1044761216230914</v>
+        <v>0.1045145412627287</v>
       </c>
       <c r="C12">
-        <v>977.6563219251948</v>
+        <v>966.7755783095168</v>
       </c>
       <c r="D12">
-        <v>1044.926321925195</v>
+        <v>1044.242578309517</v>
       </c>
       <c r="E12">
-        <v>-276.63</v>
+        <v>-266.433</v>
       </c>
       <c r="F12">
-        <v>101.97</v>
+        <v>112.167</v>
       </c>
       <c r="G12">
         <v>34.7</v>
@@ -2271,45 +2271,45 @@
         <v>53.8</v>
       </c>
       <c r="M12">
-        <v>5.282046</v>
+        <v>6.0009345</v>
       </c>
       <c r="N12">
-        <v>48.517954</v>
+        <v>47.7990655</v>
       </c>
       <c r="O12">
-        <v>7.762872639999999</v>
+        <v>7.64785048</v>
       </c>
       <c r="P12">
-        <v>40.75508136</v>
+        <v>40.15121502</v>
       </c>
       <c r="Q12">
-        <v>92.45508136000001</v>
+        <v>91.85121502</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.111249912914546</v>
+        <v>0.1118776868120547</v>
       </c>
       <c r="T12">
-        <v>0.900942686942071</v>
+        <v>0.9095842309385009</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.16</v>
       </c>
       <c r="W12">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.18544707865096</v>
+        <v>8.965270325813421</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1045145412627287</v>
+        <v>0.1044101609023659</v>
       </c>
       <c r="C13">
-        <v>966.7755783095168</v>
+        <v>958.4382970844174</v>
       </c>
       <c r="D13">
-        <v>1044.242578309517</v>
+        <v>1046.102297084417</v>
       </c>
       <c r="E13">
-        <v>-266.433</v>
+        <v>-256.236</v>
       </c>
       <c r="F13">
-        <v>112.167</v>
+        <v>122.364</v>
       </c>
       <c r="G13">
         <v>34.7</v>
@@ -2353,28 +2353,28 @@
         <v>53.8</v>
       </c>
       <c r="M13">
-        <v>6.0009345</v>
+        <v>6.546474</v>
       </c>
       <c r="N13">
-        <v>47.7990655</v>
+        <v>47.25352599999999</v>
       </c>
       <c r="O13">
-        <v>7.64785048</v>
+        <v>7.560564159999999</v>
       </c>
       <c r="P13">
-        <v>40.15121502</v>
+        <v>39.69296184</v>
       </c>
       <c r="Q13">
-        <v>91.85121502</v>
+        <v>91.39296184</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1118776868120547</v>
+        <v>0.1125197282981431</v>
       </c>
       <c r="T13">
-        <v>0.9095842309385009</v>
+        <v>0.9184221736621223</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.965270325813421</v>
+        <v>8.218164465328968</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1044101609023659</v>
+        <v>0.1043931405420032</v>
       </c>
       <c r="C14">
-        <v>958.4382970844174</v>
+        <v>948.54517289493</v>
       </c>
       <c r="D14">
-        <v>1046.102297084417</v>
+        <v>1046.40617289493</v>
       </c>
       <c r="E14">
-        <v>-256.236</v>
+        <v>-246.039</v>
       </c>
       <c r="F14">
-        <v>122.364</v>
+        <v>132.561</v>
       </c>
       <c r="G14">
         <v>34.7</v>
@@ -2435,45 +2435,45 @@
         <v>53.8</v>
       </c>
       <c r="M14">
-        <v>6.546474</v>
+        <v>7.1980623</v>
       </c>
       <c r="N14">
-        <v>47.25352599999999</v>
+        <v>46.60193769999999</v>
       </c>
       <c r="O14">
-        <v>7.560564159999999</v>
+        <v>7.456310031999999</v>
       </c>
       <c r="P14">
-        <v>39.69296184</v>
+        <v>39.145627668</v>
       </c>
       <c r="Q14">
-        <v>91.39296184</v>
+        <v>90.84562766799999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1125197282981431</v>
+        <v>0.1131765293586243</v>
       </c>
       <c r="T14">
-        <v>0.9184221736621223</v>
+        <v>0.9274632874828386</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.16</v>
       </c>
       <c r="W14">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>8.218164465328968</v>
+        <v>7.474233725373562</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1043931405420032</v>
+        <v>0.1042954801816404</v>
       </c>
       <c r="C15">
-        <v>948.54517289493</v>
+        <v>940.0951865721131</v>
       </c>
       <c r="D15">
-        <v>1046.40617289493</v>
+        <v>1048.153186572113</v>
       </c>
       <c r="E15">
-        <v>-246.039</v>
+        <v>-235.842</v>
       </c>
       <c r="F15">
-        <v>132.561</v>
+        <v>142.758</v>
       </c>
       <c r="G15">
         <v>34.7</v>
@@ -2517,28 +2517,28 @@
         <v>53.8</v>
       </c>
       <c r="M15">
-        <v>7.1980623</v>
+        <v>7.751759400000001</v>
       </c>
       <c r="N15">
-        <v>46.60193769999999</v>
+        <v>46.0482406</v>
       </c>
       <c r="O15">
-        <v>7.456310031999999</v>
+        <v>7.367718496</v>
       </c>
       <c r="P15">
-        <v>39.145627668</v>
+        <v>38.680522104</v>
       </c>
       <c r="Q15">
-        <v>90.84562766799999</v>
+        <v>90.38052210399999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1131765293586243</v>
+        <v>0.1138486048623726</v>
       </c>
       <c r="T15">
-        <v>0.9274632874828386</v>
+        <v>0.9367146597645017</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.474233725373562</v>
+        <v>6.94035988784688</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1042954801816404</v>
+        <v>0.1041978198212777</v>
       </c>
       <c r="C16">
-        <v>940.0951865721131</v>
+        <v>931.6510434121336</v>
       </c>
       <c r="D16">
-        <v>1048.153186572113</v>
+        <v>1049.906043412134</v>
       </c>
       <c r="E16">
-        <v>-235.842</v>
+        <v>-225.645</v>
       </c>
       <c r="F16">
-        <v>142.758</v>
+        <v>152.955</v>
       </c>
       <c r="G16">
         <v>34.7</v>
@@ -2599,28 +2599,28 @@
         <v>53.8</v>
       </c>
       <c r="M16">
-        <v>7.751759400000001</v>
+        <v>8.305456500000002</v>
       </c>
       <c r="N16">
-        <v>46.0482406</v>
+        <v>45.49454349999999</v>
       </c>
       <c r="O16">
-        <v>7.367718496</v>
+        <v>7.279126959999999</v>
       </c>
       <c r="P16">
-        <v>38.680522104</v>
+        <v>38.21541653999999</v>
       </c>
       <c r="Q16">
-        <v>90.38052210399999</v>
+        <v>89.91541654</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1138486048623726</v>
+        <v>0.1145364939073855</v>
       </c>
       <c r="T16">
-        <v>0.9367146597645017</v>
+        <v>0.9461837113939685</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.94035988784688</v>
+        <v>6.477669228657086</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1041978198212777</v>
+        <v>0.1042345594609149</v>
       </c>
       <c r="C17">
-        <v>931.6510434121336</v>
+        <v>920.7939345648385</v>
       </c>
       <c r="D17">
-        <v>1049.906043412134</v>
+        <v>1049.245934564839</v>
       </c>
       <c r="E17">
-        <v>-225.645</v>
+        <v>-215.448</v>
       </c>
       <c r="F17">
-        <v>152.955</v>
+        <v>163.152</v>
       </c>
       <c r="G17">
         <v>34.7</v>
@@ -2681,45 +2681,45 @@
         <v>53.8</v>
       </c>
       <c r="M17">
-        <v>8.3054565</v>
+        <v>9.022305600000001</v>
       </c>
       <c r="N17">
-        <v>45.4945435</v>
+        <v>44.77769439999999</v>
       </c>
       <c r="O17">
-        <v>7.27912696</v>
+        <v>7.164431103999999</v>
       </c>
       <c r="P17">
-        <v>38.21541654</v>
+        <v>37.61326329599999</v>
       </c>
       <c r="Q17">
-        <v>89.91541654</v>
+        <v>89.313263296</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1145364939073855</v>
+        <v>0.1152407612629939</v>
       </c>
       <c r="T17">
-        <v>0.9461837113939685</v>
+        <v>0.9558782166336608</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.16</v>
       </c>
       <c r="W17">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.477669228657088</v>
+        <v>5.962999080855783</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1042345594609149</v>
+        <v>0.1041452991005522</v>
       </c>
       <c r="C18">
-        <v>920.7939345648385</v>
+        <v>912.2021379260724</v>
       </c>
       <c r="D18">
-        <v>1049.245934564839</v>
+        <v>1050.851137926072</v>
       </c>
       <c r="E18">
-        <v>-215.448</v>
+        <v>-205.251</v>
       </c>
       <c r="F18">
-        <v>163.152</v>
+        <v>173.349</v>
       </c>
       <c r="G18">
         <v>34.7</v>
@@ -2763,28 +2763,28 @@
         <v>53.8</v>
       </c>
       <c r="M18">
-        <v>9.022305600000001</v>
+        <v>9.586199700000002</v>
       </c>
       <c r="N18">
-        <v>44.77769439999999</v>
+        <v>44.2138003</v>
       </c>
       <c r="O18">
-        <v>7.164431103999999</v>
+        <v>7.074208047999999</v>
       </c>
       <c r="P18">
-        <v>37.61326329599999</v>
+        <v>37.139592252</v>
       </c>
       <c r="Q18">
-        <v>89.313263296</v>
+        <v>88.839592252</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1152407612629939</v>
+        <v>0.1159619989163279</v>
       </c>
       <c r="T18">
-        <v>0.9558782166336608</v>
+        <v>0.9658063244092494</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.962999080855783</v>
+        <v>5.612234429040737</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1041452991005522</v>
+        <v>0.1040560387401894</v>
       </c>
       <c r="C19">
-        <v>912.2021379260724</v>
+        <v>903.6152602977158</v>
       </c>
       <c r="D19">
-        <v>1050.851137926072</v>
+        <v>1052.461260297716</v>
       </c>
       <c r="E19">
-        <v>-205.251</v>
+        <v>-195.054</v>
       </c>
       <c r="F19">
-        <v>173.349</v>
+        <v>183.546</v>
       </c>
       <c r="G19">
         <v>34.7</v>
@@ -2845,28 +2845,28 @@
         <v>53.8</v>
       </c>
       <c r="M19">
-        <v>9.586199700000002</v>
+        <v>10.1500938</v>
       </c>
       <c r="N19">
-        <v>44.2138003</v>
+        <v>43.6499062</v>
       </c>
       <c r="O19">
-        <v>7.074208047999999</v>
+        <v>6.983984992</v>
       </c>
       <c r="P19">
-        <v>37.139592252</v>
+        <v>36.665921208</v>
       </c>
       <c r="Q19">
-        <v>88.839592252</v>
+        <v>88.365921208</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1159619989163279</v>
+        <v>0.1167008277319383</v>
       </c>
       <c r="T19">
-        <v>0.9658063244092494</v>
+        <v>0.9759765811549741</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.612234429040737</v>
+        <v>5.300443627427363</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1040560387401894</v>
+        <v>0.1039667783798267</v>
       </c>
       <c r="C20">
-        <v>903.6152602977156</v>
+        <v>895.0333243253048</v>
       </c>
       <c r="D20">
-        <v>1052.461260297716</v>
+        <v>1054.076324325305</v>
       </c>
       <c r="E20">
-        <v>-195.054</v>
+        <v>-184.857</v>
       </c>
       <c r="F20">
-        <v>183.546</v>
+        <v>193.743</v>
       </c>
       <c r="G20">
         <v>34.7</v>
@@ -2927,28 +2927,28 @@
         <v>53.8</v>
       </c>
       <c r="M20">
-        <v>10.1500938</v>
+        <v>10.7139879</v>
       </c>
       <c r="N20">
-        <v>43.6499062</v>
+        <v>43.0860121</v>
       </c>
       <c r="O20">
-        <v>6.983984992</v>
+        <v>6.893761936</v>
       </c>
       <c r="P20">
-        <v>36.665921208</v>
+        <v>36.192250164</v>
       </c>
       <c r="Q20">
-        <v>88.365921208</v>
+        <v>87.892250164</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1167008277319383</v>
+        <v>0.1174578992343539</v>
       </c>
       <c r="T20">
-        <v>0.9759765811549741</v>
+        <v>0.9863979553512106</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.300443627427364</v>
+        <v>5.021472910194344</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1039667783798267</v>
+        <v>0.1038775180194639</v>
       </c>
       <c r="C21">
-        <v>895.0333243253048</v>
+        <v>886.4563527935941</v>
       </c>
       <c r="D21">
-        <v>1054.076324325305</v>
+        <v>1055.696352793594</v>
       </c>
       <c r="E21">
-        <v>-184.857</v>
+        <v>-174.66</v>
       </c>
       <c r="F21">
-        <v>193.743</v>
+        <v>203.94</v>
       </c>
       <c r="G21">
         <v>34.7</v>
@@ -3009,28 +3009,28 @@
         <v>53.8</v>
       </c>
       <c r="M21">
-        <v>10.7139879</v>
+        <v>11.277882</v>
       </c>
       <c r="N21">
-        <v>43.0860121</v>
+        <v>42.52211799999999</v>
       </c>
       <c r="O21">
-        <v>6.893761936</v>
+        <v>6.803538879999999</v>
       </c>
       <c r="P21">
-        <v>36.192250164</v>
+        <v>35.71857911999999</v>
       </c>
       <c r="Q21">
-        <v>87.892250164</v>
+        <v>87.41857912</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1174578992343539</v>
+        <v>0.1182338975243299</v>
       </c>
       <c r="T21">
-        <v>0.9863979553512106</v>
+        <v>0.997079863902353</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.021472910194344</v>
+        <v>4.770399264684626</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1038775180194639</v>
+        <v>0.1037882576591012</v>
       </c>
       <c r="C22">
-        <v>886.4563527935941</v>
+        <v>877.8843686276267</v>
       </c>
       <c r="D22">
-        <v>1055.696352793594</v>
+        <v>1057.321368627627</v>
       </c>
       <c r="E22">
-        <v>-174.66</v>
+        <v>-164.463</v>
       </c>
       <c r="F22">
-        <v>203.94</v>
+        <v>214.137</v>
       </c>
       <c r="G22">
         <v>34.7</v>
@@ -3091,28 +3091,28 @@
         <v>53.8</v>
       </c>
       <c r="M22">
-        <v>11.277882</v>
+        <v>11.8417761</v>
       </c>
       <c r="N22">
-        <v>42.52211799999999</v>
+        <v>41.95822389999999</v>
       </c>
       <c r="O22">
-        <v>6.803538879999999</v>
+        <v>6.713315823999999</v>
       </c>
       <c r="P22">
-        <v>35.71857911999999</v>
+        <v>35.24490807599999</v>
       </c>
       <c r="Q22">
-        <v>87.41857912</v>
+        <v>86.94490807599999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1182338975243299</v>
+        <v>0.1190295413406344</v>
       </c>
       <c r="T22">
-        <v>0.997079863902353</v>
+        <v>1.008032200518082</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.770399264684626</v>
+        <v>4.543237394937739</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1037882576591012</v>
+        <v>0.1041609972987384</v>
       </c>
       <c r="C23">
-        <v>877.8843686276268</v>
+        <v>860.9344753570463</v>
       </c>
       <c r="D23">
-        <v>1057.321368627627</v>
+        <v>1050.568475357046</v>
       </c>
       <c r="E23">
-        <v>-164.463</v>
+        <v>-154.266</v>
       </c>
       <c r="F23">
-        <v>214.137</v>
+        <v>224.334</v>
       </c>
       <c r="G23">
         <v>34.7</v>
@@ -3173,45 +3173,45 @@
         <v>53.8</v>
       </c>
       <c r="M23">
-        <v>11.8417761</v>
+        <v>12.9665052</v>
       </c>
       <c r="N23">
-        <v>41.95822389999999</v>
+        <v>40.8334948</v>
       </c>
       <c r="O23">
-        <v>6.713315823999999</v>
+        <v>6.533359168</v>
       </c>
       <c r="P23">
-        <v>35.24490807599999</v>
+        <v>34.300135632</v>
       </c>
       <c r="Q23">
-        <v>86.94490807599999</v>
+        <v>86.000135632</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1190295413406344</v>
+        <v>0.1198455862804338</v>
       </c>
       <c r="T23">
-        <v>1.008032200518082</v>
+        <v>1.019265366277803</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.16</v>
       </c>
       <c r="W23">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.543237394937741</v>
+        <v>4.149151924143754</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1041609972987384</v>
+        <v>0.1047689369383757</v>
       </c>
       <c r="C24">
-        <v>860.9344753570463</v>
+        <v>839.9066506299483</v>
       </c>
       <c r="D24">
-        <v>1050.568475357046</v>
+        <v>1039.737650629948</v>
       </c>
       <c r="E24">
-        <v>-154.266</v>
+        <v>-144.069</v>
       </c>
       <c r="F24">
-        <v>224.334</v>
+        <v>234.531</v>
       </c>
       <c r="G24">
         <v>34.7</v>
@@ -3255,45 +3255,45 @@
         <v>53.8</v>
       </c>
       <c r="M24">
-        <v>12.9665052</v>
+        <v>14.3767503</v>
       </c>
       <c r="N24">
-        <v>40.8334948</v>
+        <v>39.42324969999999</v>
       </c>
       <c r="O24">
-        <v>6.533359168</v>
+        <v>6.307719951999999</v>
       </c>
       <c r="P24">
-        <v>34.300135632</v>
+        <v>33.11552974799999</v>
       </c>
       <c r="Q24">
-        <v>86.000135632</v>
+        <v>84.81552974799999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1198455862804338</v>
+        <v>0.1206828271926957</v>
       </c>
       <c r="T24">
-        <v>1.019265366277803</v>
+        <v>1.030790302576738</v>
       </c>
       <c r="U24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.16</v>
       </c>
       <c r="W24">
-        <v>0.048552</v>
+        <v>0.051492</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.149151924143754</v>
+        <v>3.742153051096671</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1047689369383757</v>
+        <v>0.1047300765780129</v>
       </c>
       <c r="C25">
-        <v>839.9066506299483</v>
+        <v>830.3952865926424</v>
       </c>
       <c r="D25">
-        <v>1039.737650629948</v>
+        <v>1040.423286592642</v>
       </c>
       <c r="E25">
-        <v>-144.069</v>
+        <v>-133.872</v>
       </c>
       <c r="F25">
-        <v>234.531</v>
+        <v>244.728</v>
       </c>
       <c r="G25">
         <v>34.7</v>
@@ -3337,28 +3337,28 @@
         <v>53.8</v>
       </c>
       <c r="M25">
-        <v>14.3767503</v>
+        <v>15.0018264</v>
       </c>
       <c r="N25">
-        <v>39.42324969999999</v>
+        <v>38.7981736</v>
       </c>
       <c r="O25">
-        <v>6.307719951999999</v>
+        <v>6.207707775999999</v>
       </c>
       <c r="P25">
-        <v>33.11552974799999</v>
+        <v>32.590465824</v>
       </c>
       <c r="Q25">
-        <v>84.81552974799999</v>
+        <v>84.29046582399999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1206828271926957</v>
+        <v>0.1215421007605433</v>
       </c>
       <c r="T25">
-        <v>1.030790302576738</v>
+        <v>1.042618526673013</v>
       </c>
       <c r="U25">
         <v>0.0613</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.742153051096671</v>
+        <v>3.586230007300977</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1047300765780129</v>
+        <v>0.1052792162176502</v>
       </c>
       <c r="C26">
-        <v>830.3952865926426</v>
+        <v>810.5926175034767</v>
       </c>
       <c r="D26">
-        <v>1040.423286592643</v>
+        <v>1030.817617503477</v>
       </c>
       <c r="E26">
-        <v>-133.872</v>
+        <v>-123.675</v>
       </c>
       <c r="F26">
-        <v>244.728</v>
+        <v>254.925</v>
       </c>
       <c r="G26">
         <v>34.7</v>
@@ -3419,45 +3419,45 @@
         <v>53.8</v>
       </c>
       <c r="M26">
-        <v>15.0018264</v>
+        <v>16.3406925</v>
       </c>
       <c r="N26">
-        <v>38.7981736</v>
+        <v>37.45930749999999</v>
       </c>
       <c r="O26">
-        <v>6.207707775999999</v>
+        <v>5.993489199999999</v>
       </c>
       <c r="P26">
-        <v>32.590465824</v>
+        <v>31.4658183</v>
       </c>
       <c r="Q26">
-        <v>84.29046582399999</v>
+        <v>83.1658183</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1215421007605433</v>
+        <v>0.1224242882902002</v>
       </c>
       <c r="T26">
-        <v>1.042618526673013</v>
+        <v>1.054762170078522</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.16</v>
       </c>
       <c r="W26">
-        <v>0.051492</v>
+        <v>0.053844</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.586230007300978</v>
+        <v>3.292394125891543</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1052792162176502</v>
+        <v>0.1052638758572874</v>
       </c>
       <c r="C27">
-        <v>810.5926175034767</v>
+        <v>800.6615455731289</v>
       </c>
       <c r="D27">
-        <v>1030.817617503477</v>
+        <v>1031.083545573129</v>
       </c>
       <c r="E27">
-        <v>-123.675</v>
+        <v>-113.478</v>
       </c>
       <c r="F27">
-        <v>254.925</v>
+        <v>265.122</v>
       </c>
       <c r="G27">
         <v>34.7</v>
@@ -3501,28 +3501,28 @@
         <v>53.8</v>
       </c>
       <c r="M27">
-        <v>16.3406925</v>
+        <v>16.9943202</v>
       </c>
       <c r="N27">
-        <v>37.45930749999999</v>
+        <v>36.80567979999999</v>
       </c>
       <c r="O27">
-        <v>5.993489199999999</v>
+        <v>5.888908767999999</v>
       </c>
       <c r="P27">
-        <v>31.4658183</v>
+        <v>30.91677103199999</v>
       </c>
       <c r="Q27">
-        <v>83.1658183</v>
+        <v>82.616771032</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1224242882902002</v>
+        <v>0.1233303187260641</v>
       </c>
       <c r="T27">
-        <v>1.054762170078522</v>
+        <v>1.067234020062559</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.292394125891543</v>
+        <v>3.165763582588022</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1052638758572874</v>
+        <v>0.1052485354969247</v>
       </c>
       <c r="C28">
-        <v>800.6615455731289</v>
+        <v>790.7306108852683</v>
       </c>
       <c r="D28">
-        <v>1031.083545573129</v>
+        <v>1031.349610885268</v>
       </c>
       <c r="E28">
-        <v>-113.478</v>
+        <v>-103.281</v>
       </c>
       <c r="F28">
-        <v>265.122</v>
+        <v>275.319</v>
       </c>
       <c r="G28">
         <v>34.7</v>
@@ -3583,28 +3583,28 @@
         <v>53.8</v>
       </c>
       <c r="M28">
-        <v>16.9943202</v>
+        <v>17.6479479</v>
       </c>
       <c r="N28">
-        <v>36.80567979999999</v>
+        <v>36.15205209999999</v>
       </c>
       <c r="O28">
-        <v>5.888908767999999</v>
+        <v>5.784328335999999</v>
       </c>
       <c r="P28">
-        <v>30.91677103199999</v>
+        <v>30.36772376399999</v>
       </c>
       <c r="Q28">
-        <v>82.616771032</v>
+        <v>82.06772376399999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1233303187260641</v>
+        <v>0.1242611719135954</v>
       </c>
       <c r="T28">
-        <v>1.067234020062559</v>
+        <v>1.080047564566706</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.165763582588022</v>
+        <v>3.048513079529206</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1052485354969247</v>
+        <v>0.1070677551365619</v>
       </c>
       <c r="C29">
-        <v>790.7306108852683</v>
+        <v>749.9098110859663</v>
       </c>
       <c r="D29">
-        <v>1031.349610885268</v>
+        <v>1000.725811085966</v>
       </c>
       <c r="E29">
-        <v>-103.281</v>
+        <v>-93.084</v>
       </c>
       <c r="F29">
-        <v>275.319</v>
+        <v>285.516</v>
       </c>
       <c r="G29">
         <v>34.7</v>
@@ -3665,45 +3665,45 @@
         <v>53.8</v>
       </c>
       <c r="M29">
-        <v>17.6479479</v>
+        <v>20.5286004</v>
       </c>
       <c r="N29">
-        <v>36.15205209999999</v>
+        <v>33.2713996</v>
       </c>
       <c r="O29">
-        <v>5.784328335999999</v>
+        <v>5.323423935999999</v>
       </c>
       <c r="P29">
-        <v>30.36772376399999</v>
+        <v>27.947975664</v>
       </c>
       <c r="Q29">
-        <v>82.06772376399999</v>
+        <v>79.647975664</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1242611719135954</v>
+        <v>0.1252178821341138</v>
       </c>
       <c r="T29">
-        <v>1.080047564566706</v>
+        <v>1.093217040862635</v>
       </c>
       <c r="U29">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V29">
         <v>0.16</v>
       </c>
       <c r="W29">
-        <v>0.053844</v>
+        <v>0.06039600000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.048513079529206</v>
+        <v>2.620733949305185</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1070677551365619</v>
+        <v>0.1071179347761992</v>
       </c>
       <c r="C30">
-        <v>749.9098110859663</v>
+        <v>738.8938653605555</v>
       </c>
       <c r="D30">
-        <v>1000.725811085966</v>
+        <v>999.9068653605555</v>
       </c>
       <c r="E30">
-        <v>-93.084</v>
+        <v>-82.887</v>
       </c>
       <c r="F30">
-        <v>285.516</v>
+        <v>295.713</v>
       </c>
       <c r="G30">
         <v>34.7</v>
@@ -3747,28 +3747,28 @@
         <v>53.8</v>
       </c>
       <c r="M30">
-        <v>20.5286004</v>
+        <v>21.2617647</v>
       </c>
       <c r="N30">
-        <v>33.2713996</v>
+        <v>32.5382353</v>
       </c>
       <c r="O30">
-        <v>5.323423935999999</v>
+        <v>5.206117647999999</v>
       </c>
       <c r="P30">
-        <v>27.947975664</v>
+        <v>27.332117652</v>
       </c>
       <c r="Q30">
-        <v>79.647975664</v>
+        <v>79.032117652</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1252178821341138</v>
+        <v>0.1262015419383087</v>
       </c>
       <c r="T30">
-        <v>1.093217040862635</v>
+        <v>1.10675748832183</v>
       </c>
       <c r="U30">
         <v>0.07190000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.620733949305185</v>
+        <v>2.530363813122247</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1071179347761991</v>
+        <v>0.1081509144158364</v>
       </c>
       <c r="C31">
-        <v>738.8938653605558</v>
+        <v>712.1312152313153</v>
       </c>
       <c r="D31">
-        <v>999.9068653605557</v>
+        <v>983.3412152313153</v>
       </c>
       <c r="E31">
-        <v>-82.88700000000006</v>
+        <v>-72.69</v>
       </c>
       <c r="F31">
-        <v>295.713</v>
+        <v>305.91</v>
       </c>
       <c r="G31">
         <v>34.7</v>
@@ -3829,45 +3829,45 @@
         <v>53.8</v>
       </c>
       <c r="M31">
-        <v>21.2617647</v>
+        <v>23.187978</v>
       </c>
       <c r="N31">
-        <v>32.5382353</v>
+        <v>30.61202199999999</v>
       </c>
       <c r="O31">
-        <v>5.206117647999999</v>
+        <v>4.897923519999999</v>
       </c>
       <c r="P31">
-        <v>27.332117652</v>
+        <v>25.71409847999999</v>
       </c>
       <c r="Q31">
-        <v>79.032117652</v>
+        <v>77.41409847999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1262015419383087</v>
+        <v>0.1272133063083377</v>
       </c>
       <c r="T31">
-        <v>1.10675748832183</v>
+        <v>1.12068480570843</v>
       </c>
       <c r="U31">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V31">
         <v>0.16</v>
       </c>
       <c r="W31">
-        <v>0.06039600000000001</v>
+        <v>0.06367200000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.530363813122247</v>
+        <v>2.320167804195777</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1081509144158364</v>
+        <v>0.1082338540554736</v>
       </c>
       <c r="C32">
-        <v>712.1312152313153</v>
+        <v>700.6279052610982</v>
       </c>
       <c r="D32">
-        <v>983.3412152313153</v>
+        <v>982.0349052610982</v>
       </c>
       <c r="E32">
-        <v>-72.69</v>
+        <v>-62.49299999999999</v>
       </c>
       <c r="F32">
-        <v>305.91</v>
+        <v>316.107</v>
       </c>
       <c r="G32">
         <v>34.7</v>
@@ -3911,28 +3911,28 @@
         <v>53.8</v>
       </c>
       <c r="M32">
-        <v>23.187978</v>
+        <v>23.96091060000001</v>
       </c>
       <c r="N32">
-        <v>30.61202199999999</v>
+        <v>29.83908939999999</v>
       </c>
       <c r="O32">
-        <v>4.897923519999999</v>
+        <v>4.774254303999999</v>
       </c>
       <c r="P32">
-        <v>25.71409847999999</v>
+        <v>25.06483509599999</v>
       </c>
       <c r="Q32">
-        <v>77.41409847999999</v>
+        <v>76.764835096</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1272133063083377</v>
+        <v>0.1282543971818459</v>
       </c>
       <c r="T32">
-        <v>1.12068480570843</v>
+        <v>1.135015813454062</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.320167804195777</v>
+        <v>2.245323681479784</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1082338540554736</v>
+        <v>0.1083167936951109</v>
       </c>
       <c r="C33">
-        <v>700.6279052610982</v>
+        <v>689.1280613956435</v>
       </c>
       <c r="D33">
-        <v>982.0349052610982</v>
+        <v>980.7320613956435</v>
       </c>
       <c r="E33">
-        <v>-62.49299999999999</v>
+        <v>-52.29599999999999</v>
       </c>
       <c r="F33">
-        <v>316.107</v>
+        <v>326.304</v>
       </c>
       <c r="G33">
         <v>34.7</v>
@@ -3993,28 +3993,28 @@
         <v>53.8</v>
       </c>
       <c r="M33">
-        <v>23.96091060000001</v>
+        <v>24.7338432</v>
       </c>
       <c r="N33">
-        <v>29.83908939999999</v>
+        <v>29.06615679999999</v>
       </c>
       <c r="O33">
-        <v>4.774254303999999</v>
+        <v>4.650585087999999</v>
       </c>
       <c r="P33">
-        <v>25.06483509599999</v>
+        <v>24.41557171199999</v>
       </c>
       <c r="Q33">
-        <v>76.764835096</v>
+        <v>76.11557171199999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1282543971818459</v>
+        <v>0.1293261083751631</v>
       </c>
       <c r="T33">
-        <v>1.135015813454062</v>
+        <v>1.149768321427507</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.245323681479784</v>
+        <v>2.175157316433541</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1083167936951109</v>
+        <v>0.1083997333347481</v>
       </c>
       <c r="C34">
-        <v>689.1280613956435</v>
+        <v>677.6316698580172</v>
       </c>
       <c r="D34">
-        <v>980.7320613956435</v>
+        <v>979.4326698580172</v>
       </c>
       <c r="E34">
-        <v>-52.29599999999999</v>
+        <v>-42.09899999999999</v>
       </c>
       <c r="F34">
-        <v>326.304</v>
+        <v>336.501</v>
       </c>
       <c r="G34">
         <v>34.7</v>
@@ -4075,28 +4075,28 @@
         <v>53.8</v>
       </c>
       <c r="M34">
-        <v>24.7338432</v>
+        <v>25.5067758</v>
       </c>
       <c r="N34">
-        <v>29.06615679999999</v>
+        <v>28.29322419999999</v>
       </c>
       <c r="O34">
-        <v>4.650585087999999</v>
+        <v>4.526915871999999</v>
       </c>
       <c r="P34">
-        <v>24.41557171199999</v>
+        <v>23.76630832799999</v>
       </c>
       <c r="Q34">
-        <v>76.11557171199999</v>
+        <v>75.466308328</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1293261083751631</v>
+        <v>0.1304298109473853</v>
       </c>
       <c r="T34">
-        <v>1.149768321427507</v>
+        <v>1.164961202773293</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.175157316433541</v>
+        <v>2.109243458359797</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1083997333347481</v>
+        <v>0.1084826729743854</v>
       </c>
       <c r="C35">
-        <v>677.6316698580172</v>
+        <v>666.1387169442003</v>
       </c>
       <c r="D35">
-        <v>979.4326698580172</v>
+        <v>978.1367169442003</v>
       </c>
       <c r="E35">
-        <v>-42.09899999999999</v>
+        <v>-31.90199999999999</v>
       </c>
       <c r="F35">
-        <v>336.501</v>
+        <v>346.698</v>
       </c>
       <c r="G35">
         <v>34.7</v>
@@ -4157,28 +4157,28 @@
         <v>53.8</v>
       </c>
       <c r="M35">
-        <v>25.5067758</v>
+        <v>26.2797084</v>
       </c>
       <c r="N35">
-        <v>28.29322419999999</v>
+        <v>27.52029159999999</v>
       </c>
       <c r="O35">
-        <v>4.526915871999999</v>
+        <v>4.403246655999999</v>
       </c>
       <c r="P35">
-        <v>23.76630832799999</v>
+        <v>23.11704494399999</v>
       </c>
       <c r="Q35">
-        <v>75.466308328</v>
+        <v>74.817044944</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1304298109473853</v>
+        <v>0.1315669590520991</v>
       </c>
       <c r="T35">
-        <v>1.164961202773293</v>
+        <v>1.180614474462891</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.109243458359797</v>
+        <v>2.047206886055098</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1084826729743854</v>
+        <v>0.1127404126140227</v>
       </c>
       <c r="C36">
-        <v>666.1387169442003</v>
+        <v>593.7274085751847</v>
       </c>
       <c r="D36">
-        <v>978.1367169442003</v>
+        <v>915.9224085751846</v>
       </c>
       <c r="E36">
-        <v>-31.90199999999999</v>
+        <v>-21.70499999999998</v>
       </c>
       <c r="F36">
-        <v>346.698</v>
+        <v>356.895</v>
       </c>
       <c r="G36">
         <v>34.7</v>
@@ -4239,45 +4239,45 @@
         <v>53.8</v>
       </c>
       <c r="M36">
-        <v>26.2797084</v>
+        <v>32.12055</v>
       </c>
       <c r="N36">
-        <v>27.52029159999999</v>
+        <v>21.67945</v>
       </c>
       <c r="O36">
-        <v>4.403246655999999</v>
+        <v>3.468712</v>
       </c>
       <c r="P36">
-        <v>23.11704494399999</v>
+        <v>18.210738</v>
       </c>
       <c r="Q36">
-        <v>74.817044944</v>
+        <v>69.91073799999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1315669590520991</v>
+        <v>0.1327390963292656</v>
       </c>
       <c r="T36">
-        <v>1.180614474462891</v>
+        <v>1.1967493852814</v>
       </c>
       <c r="U36">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V36">
         <v>0.16</v>
       </c>
       <c r="W36">
-        <v>0.06367200000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.047206886055098</v>
+        <v>1.674940186267047</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1127404126140227</v>
+        <v>0.1129426322536599</v>
       </c>
       <c r="C37">
-        <v>593.7274085751847</v>
+        <v>580.7718408339317</v>
       </c>
       <c r="D37">
-        <v>915.9224085751846</v>
+        <v>913.1638408339317</v>
       </c>
       <c r="E37">
-        <v>-21.70499999999998</v>
+        <v>-11.50799999999998</v>
       </c>
       <c r="F37">
-        <v>356.895</v>
+        <v>367.092</v>
       </c>
       <c r="G37">
         <v>34.7</v>
@@ -4321,28 +4321,28 @@
         <v>53.8</v>
       </c>
       <c r="M37">
-        <v>32.12055</v>
+        <v>33.03828</v>
       </c>
       <c r="N37">
-        <v>21.67945</v>
+        <v>20.76172</v>
       </c>
       <c r="O37">
-        <v>3.468712</v>
+        <v>3.3218752</v>
       </c>
       <c r="P37">
-        <v>18.210738</v>
+        <v>17.4398448</v>
       </c>
       <c r="Q37">
-        <v>69.91073799999999</v>
+        <v>69.13984479999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1327390963292656</v>
+        <v>0.1339478628963436</v>
       </c>
       <c r="T37">
-        <v>1.1967493852814</v>
+        <v>1.213388512062988</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.674940186267047</v>
+        <v>1.628414069981851</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1129426322536599</v>
+        <v>0.1131448518932971</v>
       </c>
       <c r="C38">
-        <v>580.7718408339317</v>
+        <v>567.832839661878</v>
       </c>
       <c r="D38">
-        <v>913.1638408339317</v>
+        <v>910.4218396618779</v>
       </c>
       <c r="E38">
-        <v>-11.50800000000004</v>
+        <v>-1.311000000000035</v>
       </c>
       <c r="F38">
-        <v>367.092</v>
+        <v>377.289</v>
       </c>
       <c r="G38">
         <v>34.7</v>
@@ -4403,28 +4403,28 @@
         <v>53.8</v>
       </c>
       <c r="M38">
-        <v>33.03828</v>
+        <v>33.95601</v>
       </c>
       <c r="N38">
-        <v>20.76172</v>
+        <v>19.84399</v>
       </c>
       <c r="O38">
-        <v>3.3218752</v>
+        <v>3.1750384</v>
       </c>
       <c r="P38">
-        <v>17.4398448</v>
+        <v>16.6689516</v>
       </c>
       <c r="Q38">
-        <v>69.13984479999999</v>
+        <v>68.3689516</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1339478628963436</v>
+        <v>0.1351950030052336</v>
       </c>
       <c r="T38">
-        <v>1.213388512062987</v>
+        <v>1.230555865091609</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.628414069981851</v>
+        <v>1.584402878901261</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1131448518932971</v>
+        <v>0.1133470715329344</v>
       </c>
       <c r="C39">
-        <v>567.832839661878</v>
+        <v>554.9102562700866</v>
       </c>
       <c r="D39">
-        <v>910.4218396618779</v>
+        <v>907.6962562700866</v>
       </c>
       <c r="E39">
-        <v>-1.311000000000035</v>
+        <v>8.886000000000024</v>
       </c>
       <c r="F39">
-        <v>377.289</v>
+        <v>387.486</v>
       </c>
       <c r="G39">
         <v>34.7</v>
@@ -4485,28 +4485,28 @@
         <v>53.8</v>
       </c>
       <c r="M39">
-        <v>33.95601</v>
+        <v>34.87374000000001</v>
       </c>
       <c r="N39">
-        <v>19.84399</v>
+        <v>18.92625999999999</v>
       </c>
       <c r="O39">
-        <v>3.1750384</v>
+        <v>3.028201599999999</v>
       </c>
       <c r="P39">
-        <v>16.6689516</v>
+        <v>15.89805839999999</v>
       </c>
       <c r="Q39">
-        <v>68.3689516</v>
+        <v>67.5980584</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1351950030052336</v>
+        <v>0.1364823734402168</v>
       </c>
       <c r="T39">
-        <v>1.230555865091609</v>
+        <v>1.248277003701799</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.584402878901261</v>
+        <v>1.542708066298596</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1133470715329344</v>
+        <v>0.1135492911725716</v>
       </c>
       <c r="C40">
-        <v>554.9102562700866</v>
+        <v>542.0039436460554</v>
       </c>
       <c r="D40">
-        <v>907.6962562700866</v>
+        <v>904.9869436460555</v>
       </c>
       <c r="E40">
-        <v>8.886000000000024</v>
+        <v>19.08300000000003</v>
       </c>
       <c r="F40">
-        <v>387.486</v>
+        <v>397.683</v>
       </c>
       <c r="G40">
         <v>34.7</v>
@@ -4567,28 +4567,28 @@
         <v>53.8</v>
       </c>
       <c r="M40">
-        <v>34.87374000000001</v>
+        <v>35.79147</v>
       </c>
       <c r="N40">
-        <v>18.92625999999999</v>
+        <v>18.00852999999999</v>
       </c>
       <c r="O40">
-        <v>3.028201599999999</v>
+        <v>2.881364799999999</v>
       </c>
       <c r="P40">
-        <v>15.89805839999999</v>
+        <v>15.12716519999999</v>
       </c>
       <c r="Q40">
-        <v>67.5980584</v>
+        <v>66.8271652</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1364823734402168</v>
+        <v>0.1378119527419207</v>
       </c>
       <c r="T40">
-        <v>1.248277003701799</v>
+        <v>1.266579163250029</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.542708066298596</v>
+        <v>1.503151449214017</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1135492911725716</v>
+        <v>0.1341786351342945</v>
       </c>
       <c r="C41">
-        <v>542.0039436460554</v>
+        <v>320.5648610660958</v>
       </c>
       <c r="D41">
-        <v>904.9869436460555</v>
+        <v>693.7448610660958</v>
       </c>
       <c r="E41">
-        <v>19.08300000000003</v>
+        <v>29.28000000000003</v>
       </c>
       <c r="F41">
-        <v>397.683</v>
+        <v>407.8800000000001</v>
       </c>
       <c r="G41">
         <v>34.7</v>
@@ -4649,45 +4649,45 @@
         <v>53.8</v>
       </c>
       <c r="M41">
-        <v>35.79147</v>
+        <v>59.87678400000001</v>
       </c>
       <c r="N41">
-        <v>18.00852999999999</v>
+        <v>-6.076784000000018</v>
       </c>
       <c r="O41">
-        <v>2.881364799999999</v>
+        <v>-0.9722854400000028</v>
       </c>
       <c r="P41">
-        <v>15.12716519999999</v>
+        <v>-5.104498560000015</v>
       </c>
       <c r="Q41">
-        <v>66.8271652</v>
+        <v>46.59550143999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1378119527419207</v>
+        <v>0.139833889455134</v>
       </c>
       <c r="T41">
-        <v>1.266579163250029</v>
+        <v>1.294411883174463</v>
       </c>
       <c r="U41">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.16</v>
+        <v>0.1437618960964904</v>
       </c>
       <c r="W41">
-        <v>0.0756</v>
+        <v>0.1256957536530352</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.503151449214017</v>
+        <v>0.8985118506030648</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1341786351342945</v>
+        <v>0.1351886351342945</v>
       </c>
       <c r="C42">
-        <v>320.5648610660958</v>
+        <v>302.5292548649376</v>
       </c>
       <c r="D42">
-        <v>693.7448610660958</v>
+        <v>685.9062548649376</v>
       </c>
       <c r="E42">
-        <v>29.28000000000003</v>
+        <v>39.47700000000003</v>
       </c>
       <c r="F42">
-        <v>407.8800000000001</v>
+        <v>418.0770000000001</v>
       </c>
       <c r="G42">
         <v>34.7</v>
@@ -4731,37 +4731,37 @@
         <v>53.8</v>
       </c>
       <c r="M42">
-        <v>59.87678400000001</v>
+        <v>61.37370360000001</v>
       </c>
       <c r="N42">
-        <v>-6.076784000000018</v>
+        <v>-7.573703600000016</v>
       </c>
       <c r="O42">
-        <v>-0.9722854400000028</v>
+        <v>-1.211792576000003</v>
       </c>
       <c r="P42">
-        <v>-5.104498560000015</v>
+        <v>-6.361911024000014</v>
       </c>
       <c r="Q42">
-        <v>46.59550143999999</v>
+        <v>45.33808897599999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.139833889455134</v>
+        <v>0.1414276841916617</v>
       </c>
       <c r="T42">
-        <v>1.294411883174463</v>
+        <v>1.316351067635047</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.1437618960964904</v>
+        <v>0.1402555083868199</v>
       </c>
       <c r="W42">
-        <v>0.1256957536530352</v>
+        <v>0.1262104913688148</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8985118506030648</v>
+        <v>0.8765969274176243</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1351886351342945</v>
+        <v>0.1361986351342945</v>
       </c>
       <c r="C43">
-        <v>302.5292548649376</v>
+        <v>284.6688060044051</v>
       </c>
       <c r="D43">
-        <v>685.9062548649376</v>
+        <v>678.2428060044051</v>
       </c>
       <c r="E43">
-        <v>39.47700000000003</v>
+        <v>49.67400000000004</v>
       </c>
       <c r="F43">
-        <v>418.0770000000001</v>
+        <v>428.2740000000001</v>
       </c>
       <c r="G43">
         <v>34.7</v>
@@ -4813,37 +4813,37 @@
         <v>53.8</v>
       </c>
       <c r="M43">
-        <v>61.37370360000001</v>
+        <v>62.87062320000001</v>
       </c>
       <c r="N43">
-        <v>-7.573703600000016</v>
+        <v>-9.070623200000014</v>
       </c>
       <c r="O43">
-        <v>-1.211792576000003</v>
+        <v>-1.451299712000002</v>
       </c>
       <c r="P43">
-        <v>-6.361911024000014</v>
+        <v>-7.619323488000012</v>
       </c>
       <c r="Q43">
-        <v>45.33808897599999</v>
+        <v>44.08067651199999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1414276841916617</v>
+        <v>0.14307643736738</v>
       </c>
       <c r="T43">
-        <v>1.316351067635047</v>
+        <v>1.33904677569772</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1402555083868199</v>
+        <v>0.136916091520467</v>
       </c>
       <c r="W43">
-        <v>0.1262104913688148</v>
+        <v>0.1267007177647954</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8765969274176243</v>
+        <v>0.855725572002919</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1361986351342945</v>
+        <v>0.1372086351342945</v>
       </c>
       <c r="C44">
-        <v>284.6688060044052</v>
+        <v>266.9777083947205</v>
       </c>
       <c r="D44">
-        <v>678.2428060044051</v>
+        <v>670.7487083947204</v>
       </c>
       <c r="E44">
-        <v>49.67399999999998</v>
+        <v>59.87099999999998</v>
       </c>
       <c r="F44">
-        <v>428.274</v>
+        <v>438.471</v>
       </c>
       <c r="G44">
         <v>34.7</v>
@@ -4895,37 +4895,37 @@
         <v>53.8</v>
       </c>
       <c r="M44">
-        <v>62.8706232</v>
+        <v>64.36754280000001</v>
       </c>
       <c r="N44">
-        <v>-9.070623200000007</v>
+        <v>-10.56754280000001</v>
       </c>
       <c r="O44">
-        <v>-1.451299712000001</v>
+        <v>-1.690806848000002</v>
       </c>
       <c r="P44">
-        <v>-7.619323488000006</v>
+        <v>-8.876735952000011</v>
       </c>
       <c r="Q44">
-        <v>44.080676512</v>
+        <v>42.82326404799999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.14307643736738</v>
+        <v>0.14478304153172</v>
       </c>
       <c r="T44">
-        <v>1.33904677569772</v>
+        <v>1.362538824394171</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.136916091520467</v>
+        <v>0.1337319963688283</v>
       </c>
       <c r="W44">
-        <v>0.1267007177647954</v>
+        <v>0.127168142933056</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8557255720029191</v>
+        <v>0.8358249773051767</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1372086351342945</v>
+        <v>0.1382186351342945</v>
       </c>
       <c r="C45">
-        <v>266.9777083947205</v>
+        <v>249.4504097542542</v>
       </c>
       <c r="D45">
-        <v>670.7487083947204</v>
+        <v>663.4184097542542</v>
       </c>
       <c r="E45">
-        <v>59.87099999999998</v>
+        <v>70.06799999999998</v>
       </c>
       <c r="F45">
-        <v>438.471</v>
+        <v>448.668</v>
       </c>
       <c r="G45">
         <v>34.7</v>
@@ -4977,37 +4977,37 @@
         <v>53.8</v>
       </c>
       <c r="M45">
-        <v>64.36754280000001</v>
+        <v>65.86446240000001</v>
       </c>
       <c r="N45">
-        <v>-10.56754280000001</v>
+        <v>-12.06446240000001</v>
       </c>
       <c r="O45">
-        <v>-1.690806848000002</v>
+        <v>-1.930313984000002</v>
       </c>
       <c r="P45">
-        <v>-8.876735952000011</v>
+        <v>-10.13414841600001</v>
       </c>
       <c r="Q45">
-        <v>42.82326404799999</v>
+        <v>41.56585158399999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.14478304153172</v>
+        <v>0.1465505958447864</v>
       </c>
       <c r="T45">
-        <v>1.362538824394171</v>
+        <v>1.386869874829781</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1337319963688283</v>
+        <v>0.1306926328149913</v>
       </c>
       <c r="W45">
-        <v>0.127168142933056</v>
+        <v>0.1276143215027593</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8358249773051767</v>
+        <v>0.8168289550936955</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1382186351342945</v>
+        <v>0.1644543778827829</v>
       </c>
       <c r="C46">
-        <v>249.4504097542542</v>
+        <v>92.56455559230869</v>
       </c>
       <c r="D46">
-        <v>663.4184097542542</v>
+        <v>516.7295555923087</v>
       </c>
       <c r="E46">
-        <v>70.06799999999998</v>
+        <v>80.26499999999999</v>
       </c>
       <c r="F46">
-        <v>448.668</v>
+        <v>458.865</v>
       </c>
       <c r="G46">
         <v>34.7</v>
@@ -5059,45 +5059,45 @@
         <v>53.8</v>
       </c>
       <c r="M46">
-        <v>65.86446240000001</v>
+        <v>92.14009200000001</v>
       </c>
       <c r="N46">
-        <v>-12.06446240000001</v>
+        <v>-38.34009200000001</v>
       </c>
       <c r="O46">
-        <v>-1.930313984000002</v>
+        <v>-6.134414720000002</v>
       </c>
       <c r="P46">
-        <v>-10.13414841600001</v>
+        <v>-32.20567728000001</v>
       </c>
       <c r="Q46">
-        <v>41.56585158399999</v>
+        <v>19.49432271999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1465505958447864</v>
+        <v>0.1500655934937615</v>
       </c>
       <c r="T46">
-        <v>1.386869874829781</v>
+        <v>1.435255140530554</v>
       </c>
       <c r="U46">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1306926328149913</v>
+        <v>0.09342295859656835</v>
       </c>
       <c r="W46">
-        <v>0.1276143215027593</v>
+        <v>0.1820406699138091</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.8168289550936955</v>
+        <v>0.5838934912285522</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1644543778827829</v>
+        <v>0.1660043778827829</v>
       </c>
       <c r="C47">
-        <v>92.56455559230869</v>
+        <v>75.70448037595412</v>
       </c>
       <c r="D47">
-        <v>516.7295555923087</v>
+        <v>510.0664803759542</v>
       </c>
       <c r="E47">
-        <v>80.26499999999999</v>
+        <v>90.46200000000005</v>
       </c>
       <c r="F47">
-        <v>458.865</v>
+        <v>469.0620000000001</v>
       </c>
       <c r="G47">
         <v>34.7</v>
@@ -5141,37 +5141,37 @@
         <v>53.8</v>
       </c>
       <c r="M47">
-        <v>92.14009200000001</v>
+        <v>94.18764960000001</v>
       </c>
       <c r="N47">
-        <v>-38.34009200000001</v>
+        <v>-40.38764960000002</v>
       </c>
       <c r="O47">
-        <v>-6.134414720000002</v>
+        <v>-6.462023936000003</v>
       </c>
       <c r="P47">
-        <v>-32.20567728000001</v>
+        <v>-33.92562566400002</v>
       </c>
       <c r="Q47">
-        <v>19.49432271999999</v>
+        <v>17.77437433599999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1500655934937615</v>
+        <v>0.1519964378177201</v>
       </c>
       <c r="T47">
-        <v>1.435255140530554</v>
+        <v>1.461833939429268</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.09342295859656835</v>
+        <v>0.09139202471403426</v>
       </c>
       <c r="W47">
-        <v>0.1820406699138091</v>
+        <v>0.1824484814374219</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5838934912285522</v>
+        <v>0.5712001544627141</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1660043778827829</v>
+        <v>0.1675543778827829</v>
       </c>
       <c r="C48">
-        <v>75.70448037595412</v>
+        <v>59.01405436260899</v>
       </c>
       <c r="D48">
-        <v>510.0664803759542</v>
+        <v>503.573054362609</v>
       </c>
       <c r="E48">
-        <v>90.46200000000005</v>
+        <v>100.659</v>
       </c>
       <c r="F48">
-        <v>469.0620000000001</v>
+        <v>479.2590000000001</v>
       </c>
       <c r="G48">
         <v>34.7</v>
@@ -5223,37 +5223,37 @@
         <v>53.8</v>
       </c>
       <c r="M48">
-        <v>94.18764960000001</v>
+        <v>96.23520720000002</v>
       </c>
       <c r="N48">
-        <v>-40.38764960000002</v>
+        <v>-42.43520720000002</v>
       </c>
       <c r="O48">
-        <v>-6.462023936000003</v>
+        <v>-6.789633152000004</v>
       </c>
       <c r="P48">
-        <v>-33.92562566400002</v>
+        <v>-35.64557404800001</v>
       </c>
       <c r="Q48">
-        <v>17.77437433599999</v>
+        <v>16.05442595199999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1519964378177201</v>
+        <v>0.1540001441916393</v>
       </c>
       <c r="T48">
-        <v>1.461833939429268</v>
+        <v>1.489415711871329</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.09139202471403426</v>
+        <v>0.08944751354990586</v>
       </c>
       <c r="W48">
-        <v>0.1824484814374219</v>
+        <v>0.1828389392791789</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5712001544627141</v>
+        <v>0.5590469596869116</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1675543778827829</v>
+        <v>0.1691043778827829</v>
       </c>
       <c r="C49">
-        <v>59.01405436260899</v>
+        <v>42.48687981678671</v>
       </c>
       <c r="D49">
-        <v>503.573054362609</v>
+        <v>497.2428798167867</v>
       </c>
       <c r="E49">
-        <v>100.659</v>
+        <v>110.8560000000001</v>
       </c>
       <c r="F49">
-        <v>479.2590000000001</v>
+        <v>489.4560000000001</v>
       </c>
       <c r="G49">
         <v>34.7</v>
@@ -5305,37 +5305,37 @@
         <v>53.8</v>
       </c>
       <c r="M49">
-        <v>96.23520720000002</v>
+        <v>98.28276480000002</v>
       </c>
       <c r="N49">
-        <v>-42.43520720000002</v>
+        <v>-44.48276480000003</v>
       </c>
       <c r="O49">
-        <v>-6.789633152000004</v>
+        <v>-7.117242368000005</v>
       </c>
       <c r="P49">
-        <v>-35.64557404800001</v>
+        <v>-37.36552243200002</v>
       </c>
       <c r="Q49">
-        <v>16.05442595199999</v>
+        <v>14.33447756799998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1540001441916393</v>
+        <v>0.1560809161953247</v>
       </c>
       <c r="T49">
-        <v>1.489415711871329</v>
+        <v>1.518058321715009</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.08944751354990586</v>
+        <v>0.08758402368428282</v>
       </c>
       <c r="W49">
-        <v>0.1828389392791789</v>
+        <v>0.183213128044196</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5590469596869116</v>
+        <v>0.5474001480267676</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1691043778827829</v>
+        <v>0.1706543778827829</v>
       </c>
       <c r="C50">
-        <v>42.48687981678677</v>
+        <v>26.11687670079186</v>
       </c>
       <c r="D50">
-        <v>497.2428798167867</v>
+        <v>491.0698767007918</v>
       </c>
       <c r="E50">
-        <v>110.856</v>
+        <v>121.053</v>
       </c>
       <c r="F50">
-        <v>489.456</v>
+        <v>499.653</v>
       </c>
       <c r="G50">
         <v>34.7</v>
@@ -5387,37 +5387,37 @@
         <v>53.8</v>
       </c>
       <c r="M50">
-        <v>98.28276480000001</v>
+        <v>100.3303224</v>
       </c>
       <c r="N50">
-        <v>-44.48276480000001</v>
+        <v>-46.53032240000002</v>
       </c>
       <c r="O50">
-        <v>-7.117242368000002</v>
+        <v>-7.444851584000003</v>
       </c>
       <c r="P50">
-        <v>-37.36552243200001</v>
+        <v>-39.08547081600001</v>
       </c>
       <c r="Q50">
-        <v>14.33447756799999</v>
+        <v>12.61452918399999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1560809161953247</v>
+        <v>0.1582432871011153</v>
       </c>
       <c r="T50">
-        <v>1.518058321715009</v>
+        <v>1.547824171160401</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.08758402368428284</v>
+        <v>0.08579659462950154</v>
       </c>
       <c r="W50">
-        <v>0.183213128044196</v>
+        <v>0.1835720437983961</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5474001480267676</v>
+        <v>0.5362287164343846</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1706543778827829</v>
+        <v>0.1722043778827829</v>
       </c>
       <c r="C51">
-        <v>26.11687670079186</v>
+        <v>9.89826319629708</v>
       </c>
       <c r="D51">
-        <v>491.0698767007918</v>
+        <v>485.0482631962971</v>
       </c>
       <c r="E51">
-        <v>121.053</v>
+        <v>131.25</v>
       </c>
       <c r="F51">
-        <v>499.653</v>
+        <v>509.85</v>
       </c>
       <c r="G51">
         <v>34.7</v>
@@ -5469,37 +5469,37 @@
         <v>53.8</v>
       </c>
       <c r="M51">
-        <v>100.3303224</v>
+        <v>102.37788</v>
       </c>
       <c r="N51">
-        <v>-46.53032240000002</v>
+        <v>-48.57788000000001</v>
       </c>
       <c r="O51">
-        <v>-7.444851584000003</v>
+        <v>-7.772460800000001</v>
       </c>
       <c r="P51">
-        <v>-39.08547081600001</v>
+        <v>-40.8054192</v>
       </c>
       <c r="Q51">
-        <v>12.61452918399999</v>
+        <v>10.8945808</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1582432871011153</v>
+        <v>0.1604921528431377</v>
       </c>
       <c r="T51">
-        <v>1.547824171160401</v>
+        <v>1.578780654583609</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.08579659462950154</v>
+        <v>0.08408066273691152</v>
       </c>
       <c r="W51">
-        <v>0.1835720437983961</v>
+        <v>0.1839166029224282</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5362287164343846</v>
+        <v>0.525504142105697</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1722043778827829</v>
+        <v>0.1737543778827829</v>
       </c>
       <c r="C52">
-        <v>9.89826319629708</v>
+        <v>-6.174462358345409</v>
       </c>
       <c r="D52">
-        <v>485.0482631962971</v>
+        <v>479.1725376416546</v>
       </c>
       <c r="E52">
-        <v>131.25</v>
+        <v>141.447</v>
       </c>
       <c r="F52">
-        <v>509.85</v>
+        <v>520.047</v>
       </c>
       <c r="G52">
         <v>34.7</v>
@@ -5551,37 +5551,37 @@
         <v>53.8</v>
       </c>
       <c r="M52">
-        <v>102.37788</v>
+        <v>104.4254376</v>
       </c>
       <c r="N52">
-        <v>-48.57788000000001</v>
+        <v>-50.62543760000001</v>
       </c>
       <c r="O52">
-        <v>-7.772460800000001</v>
+        <v>-8.100070016000002</v>
       </c>
       <c r="P52">
-        <v>-40.8054192</v>
+        <v>-42.52536758400001</v>
       </c>
       <c r="Q52">
-        <v>10.8945808</v>
+        <v>9.174632415999994</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1604921528431377</v>
+        <v>0.1628328090236099</v>
       </c>
       <c r="T52">
-        <v>1.578780654583609</v>
+        <v>1.611000667942458</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.08408066273691152</v>
+        <v>0.08243202229108972</v>
       </c>
       <c r="W52">
-        <v>0.1839166029224282</v>
+        <v>0.1842476499239492</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.525504142105697</v>
+        <v>0.5152001393193107</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1737543778827829</v>
+        <v>0.1753043778827829</v>
       </c>
       <c r="C53">
-        <v>-6.174462358345409</v>
+        <v>-22.10653823367079</v>
       </c>
       <c r="D53">
-        <v>479.1725376416546</v>
+        <v>473.4374617663292</v>
       </c>
       <c r="E53">
-        <v>141.447</v>
+        <v>151.644</v>
       </c>
       <c r="F53">
-        <v>520.047</v>
+        <v>530.244</v>
       </c>
       <c r="G53">
         <v>34.7</v>
@@ -5633,37 +5633,37 @@
         <v>53.8</v>
       </c>
       <c r="M53">
-        <v>104.4254376</v>
+        <v>106.4729952</v>
       </c>
       <c r="N53">
-        <v>-50.62543760000001</v>
+        <v>-52.67299520000002</v>
       </c>
       <c r="O53">
-        <v>-8.100070016000002</v>
+        <v>-8.427679232000003</v>
       </c>
       <c r="P53">
-        <v>-42.52536758400001</v>
+        <v>-44.24531596800001</v>
       </c>
       <c r="Q53">
-        <v>9.174632415999994</v>
+        <v>7.454684031999989</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1628328090236099</v>
+        <v>0.1652709925449351</v>
       </c>
       <c r="T53">
-        <v>1.611000667942458</v>
+        <v>1.644563181857926</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.08243202229108972</v>
+        <v>0.08084679109318416</v>
       </c>
       <c r="W53">
-        <v>0.1842476499239492</v>
+        <v>0.1845659643484886</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5152001393193107</v>
+        <v>0.5052924443324009</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1753043778827829</v>
+        <v>0.1957779262635304</v>
       </c>
       <c r="C54">
-        <v>-22.10653823367079</v>
+        <v>-96.93268080295462</v>
       </c>
       <c r="D54">
-        <v>473.4374617663292</v>
+        <v>408.8083191970454</v>
       </c>
       <c r="E54">
-        <v>151.644</v>
+        <v>161.841</v>
       </c>
       <c r="F54">
-        <v>530.244</v>
+        <v>540.441</v>
       </c>
       <c r="G54">
         <v>34.7</v>
@@ -5715,45 +5715,45 @@
         <v>53.8</v>
       </c>
       <c r="M54">
-        <v>106.4729952</v>
+        <v>127.4359878</v>
       </c>
       <c r="N54">
-        <v>-52.67299520000002</v>
+        <v>-73.63598780000001</v>
       </c>
       <c r="O54">
-        <v>-8.427679232000003</v>
+        <v>-11.781758048</v>
       </c>
       <c r="P54">
-        <v>-44.24531596800001</v>
+        <v>-61.85422975200001</v>
       </c>
       <c r="Q54">
-        <v>7.454684031999989</v>
+        <v>-10.15422975200001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1652709925449351</v>
+        <v>0.1686077123453538</v>
       </c>
       <c r="T54">
-        <v>1.644563181857926</v>
+        <v>1.690494385868649</v>
       </c>
       <c r="U54">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.08084679109318416</v>
+        <v>0.06754763821903689</v>
       </c>
       <c r="W54">
-        <v>0.1845659643484886</v>
+        <v>0.2198722669079511</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.5052924443324009</v>
+        <v>0.4221727388689805</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1957779262635304</v>
+        <v>0.1976779262635304</v>
       </c>
       <c r="C55">
-        <v>-96.93268080295462</v>
+        <v>-112.2438921013537</v>
       </c>
       <c r="D55">
-        <v>408.8083191970454</v>
+        <v>403.6941078986464</v>
       </c>
       <c r="E55">
-        <v>161.841</v>
+        <v>172.038</v>
       </c>
       <c r="F55">
-        <v>540.441</v>
+        <v>550.638</v>
       </c>
       <c r="G55">
         <v>34.7</v>
@@ -5797,37 +5797,37 @@
         <v>53.8</v>
       </c>
       <c r="M55">
-        <v>127.4359878</v>
+        <v>129.8404404</v>
       </c>
       <c r="N55">
-        <v>-73.63598780000001</v>
+        <v>-76.04044040000001</v>
       </c>
       <c r="O55">
-        <v>-11.781758048</v>
+        <v>-12.166470464</v>
       </c>
       <c r="P55">
-        <v>-61.85422975200001</v>
+        <v>-63.87396993600001</v>
       </c>
       <c r="Q55">
-        <v>-10.15422975200001</v>
+        <v>-12.17396993600001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1686077123453538</v>
+        <v>0.1712774452224267</v>
       </c>
       <c r="T55">
-        <v>1.690494385868649</v>
+        <v>1.727244263822316</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06754763821903689</v>
+        <v>0.06629675602979547</v>
       </c>
       <c r="W55">
-        <v>0.2198722669079511</v>
+        <v>0.2201672249281742</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4221727388689805</v>
+        <v>0.4143547251862216</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1976779262635304</v>
+        <v>0.1995779262635304</v>
       </c>
       <c r="C56">
-        <v>-112.2438921013537</v>
+        <v>-127.4287263350718</v>
       </c>
       <c r="D56">
-        <v>403.6941078986464</v>
+        <v>398.7062736649282</v>
       </c>
       <c r="E56">
-        <v>172.038</v>
+        <v>182.235</v>
       </c>
       <c r="F56">
-        <v>550.638</v>
+        <v>560.835</v>
       </c>
       <c r="G56">
         <v>34.7</v>
@@ -5879,37 +5879,37 @@
         <v>53.8</v>
       </c>
       <c r="M56">
-        <v>129.8404404</v>
+        <v>132.244893</v>
       </c>
       <c r="N56">
-        <v>-76.04044040000001</v>
+        <v>-78.44489300000002</v>
       </c>
       <c r="O56">
-        <v>-12.166470464</v>
+        <v>-12.55118288</v>
       </c>
       <c r="P56">
-        <v>-63.87396993600001</v>
+        <v>-65.89371012000002</v>
       </c>
       <c r="Q56">
-        <v>-12.17396993600001</v>
+        <v>-14.19371012000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1712774452224267</v>
+        <v>0.1740658328940362</v>
       </c>
       <c r="T56">
-        <v>1.727244263822316</v>
+        <v>1.765627469685034</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06629675602979547</v>
+        <v>0.06509136046561736</v>
       </c>
       <c r="W56">
-        <v>0.2201672249281742</v>
+        <v>0.2204514572022074</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4143547251862216</v>
+        <v>0.4068210029101085</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1995779262635304</v>
+        <v>0.2014779262635304</v>
       </c>
       <c r="C57">
-        <v>-127.4287263350718</v>
+        <v>-142.4918106807807</v>
       </c>
       <c r="D57">
-        <v>398.7062736649282</v>
+        <v>393.8401893192193</v>
       </c>
       <c r="E57">
-        <v>182.235</v>
+        <v>192.432</v>
       </c>
       <c r="F57">
-        <v>560.835</v>
+        <v>571.032</v>
       </c>
       <c r="G57">
         <v>34.7</v>
@@ -5961,37 +5961,37 @@
         <v>53.8</v>
       </c>
       <c r="M57">
-        <v>132.244893</v>
+        <v>134.6493456</v>
       </c>
       <c r="N57">
-        <v>-78.44489300000002</v>
+        <v>-80.84934560000001</v>
       </c>
       <c r="O57">
-        <v>-12.55118288</v>
+        <v>-12.935895296</v>
       </c>
       <c r="P57">
-        <v>-65.89371012000002</v>
+        <v>-67.91345030400001</v>
       </c>
       <c r="Q57">
-        <v>-14.19371012000002</v>
+        <v>-16.21345030400001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1740658328940362</v>
+        <v>0.1769809654598098</v>
       </c>
       <c r="T57">
-        <v>1.765627469685034</v>
+        <v>1.80575536672333</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06509136046561736</v>
+        <v>0.06392901474301706</v>
       </c>
       <c r="W57">
-        <v>0.2204514572022074</v>
+        <v>0.2207255383235966</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4068210029101085</v>
+        <v>0.3995563421438566</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2014779262635304</v>
+        <v>0.2033779262635304</v>
       </c>
       <c r="C58">
-        <v>-142.4918106807807</v>
+        <v>-157.4375491459327</v>
       </c>
       <c r="D58">
-        <v>393.8401893192193</v>
+        <v>389.0914508540674</v>
       </c>
       <c r="E58">
-        <v>192.432</v>
+        <v>202.629</v>
       </c>
       <c r="F58">
-        <v>571.032</v>
+        <v>581.229</v>
       </c>
       <c r="G58">
         <v>34.7</v>
@@ -6043,37 +6043,37 @@
         <v>53.8</v>
       </c>
       <c r="M58">
-        <v>134.6493456</v>
+        <v>137.0537982</v>
       </c>
       <c r="N58">
-        <v>-80.84934560000001</v>
+        <v>-83.25379820000002</v>
       </c>
       <c r="O58">
-        <v>-12.935895296</v>
+        <v>-13.320607712</v>
       </c>
       <c r="P58">
-        <v>-67.91345030400001</v>
+        <v>-69.93319048800002</v>
       </c>
       <c r="Q58">
-        <v>-16.21345030400001</v>
+        <v>-18.23319048800002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1769809654598098</v>
+        <v>0.1800316855867821</v>
       </c>
       <c r="T58">
-        <v>1.80575536672333</v>
+        <v>1.847749677577361</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06392901474301706</v>
+        <v>0.06280745308085886</v>
       </c>
       <c r="W58">
-        <v>0.2207255383235966</v>
+        <v>0.2209900025635335</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3995563421438566</v>
+        <v>0.3925465817553678</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2033779262635304</v>
+        <v>0.2052779262635304</v>
       </c>
       <c r="C59">
-        <v>-157.4375491459327</v>
+        <v>-172.2701358628123</v>
       </c>
       <c r="D59">
-        <v>389.0914508540674</v>
+        <v>384.4558641371878</v>
       </c>
       <c r="E59">
-        <v>202.629</v>
+        <v>212.826</v>
       </c>
       <c r="F59">
-        <v>581.229</v>
+        <v>591.426</v>
       </c>
       <c r="G59">
         <v>34.7</v>
@@ -6125,37 +6125,37 @@
         <v>53.8</v>
       </c>
       <c r="M59">
-        <v>137.0537982</v>
+        <v>139.4582508</v>
       </c>
       <c r="N59">
-        <v>-83.25379820000002</v>
+        <v>-85.65825080000003</v>
       </c>
       <c r="O59">
-        <v>-13.320607712</v>
+        <v>-13.70532012800001</v>
       </c>
       <c r="P59">
-        <v>-69.93319048800002</v>
+        <v>-71.95293067200002</v>
       </c>
       <c r="Q59">
-        <v>-18.23319048800002</v>
+        <v>-20.25293067200002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1800316855867821</v>
+        <v>0.1832276781007531</v>
       </c>
       <c r="T59">
-        <v>1.847749677577361</v>
+        <v>1.891743717519679</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06280745308085886</v>
+        <v>0.06172456595877508</v>
       </c>
       <c r="W59">
-        <v>0.2209900025635335</v>
+        <v>0.2212453473469208</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3925465817553678</v>
+        <v>0.3857785372423442</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2052779262635304</v>
+        <v>0.2071779262635304</v>
       </c>
       <c r="C60">
-        <v>-172.2701358628121</v>
+        <v>-186.9935674434722</v>
       </c>
       <c r="D60">
-        <v>384.4558641371878</v>
+        <v>379.9294325565278</v>
       </c>
       <c r="E60">
-        <v>212.8259999999999</v>
+        <v>223.023</v>
       </c>
       <c r="F60">
-        <v>591.4259999999999</v>
+        <v>601.623</v>
       </c>
       <c r="G60">
         <v>34.7</v>
@@ -6207,37 +6207,37 @@
         <v>53.8</v>
       </c>
       <c r="M60">
-        <v>139.4582508</v>
+        <v>141.8627034</v>
       </c>
       <c r="N60">
-        <v>-85.6582508</v>
+        <v>-88.06270340000002</v>
       </c>
       <c r="O60">
-        <v>-13.705320128</v>
+        <v>-14.090032544</v>
       </c>
       <c r="P60">
-        <v>-71.95293067200001</v>
+        <v>-73.97267085600001</v>
       </c>
       <c r="Q60">
-        <v>-20.25293067200001</v>
+        <v>-22.272670856</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1832276781007531</v>
+        <v>0.1865795726885763</v>
       </c>
       <c r="T60">
-        <v>1.891743717519679</v>
+        <v>1.93788380819089</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0617245659587751</v>
+        <v>0.06067838687472805</v>
       </c>
       <c r="W60">
-        <v>0.2212453473469208</v>
+        <v>0.2214920363749391</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3857785372423443</v>
+        <v>0.3792399179670504</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2071779262635304</v>
+        <v>0.2090779262635304</v>
       </c>
       <c r="C61">
-        <v>-186.9935674434722</v>
+        <v>-201.6116544720539</v>
       </c>
       <c r="D61">
-        <v>379.9294325565278</v>
+        <v>375.5083455279462</v>
       </c>
       <c r="E61">
-        <v>223.023</v>
+        <v>233.22</v>
       </c>
       <c r="F61">
-        <v>601.623</v>
+        <v>611.8200000000001</v>
       </c>
       <c r="G61">
         <v>34.7</v>
@@ -6289,37 +6289,37 @@
         <v>53.8</v>
       </c>
       <c r="M61">
-        <v>141.8627034</v>
+        <v>144.267156</v>
       </c>
       <c r="N61">
-        <v>-88.06270340000002</v>
+        <v>-90.46715600000003</v>
       </c>
       <c r="O61">
-        <v>-14.090032544</v>
+        <v>-14.47474496000001</v>
       </c>
       <c r="P61">
-        <v>-73.97267085600001</v>
+        <v>-75.99241104000002</v>
       </c>
       <c r="Q61">
-        <v>-22.272670856</v>
+        <v>-24.29241104000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1865795726885763</v>
+        <v>0.1900990620057908</v>
       </c>
       <c r="T61">
-        <v>1.93788380819089</v>
+        <v>1.986330903395663</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06067838687472805</v>
+        <v>0.05966708042681591</v>
       </c>
       <c r="W61">
-        <v>0.2214920363749391</v>
+        <v>0.2217305024353568</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3792399179670504</v>
+        <v>0.3729192526675994</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2090779262635304</v>
+        <v>0.2109779262635304</v>
       </c>
       <c r="C62">
-        <v>-201.6116544720539</v>
+        <v>-216.1280322039478</v>
       </c>
       <c r="D62">
-        <v>375.5083455279462</v>
+        <v>371.1889677960523</v>
       </c>
       <c r="E62">
-        <v>233.22</v>
+        <v>243.417</v>
       </c>
       <c r="F62">
-        <v>611.8200000000001</v>
+        <v>622.0170000000001</v>
       </c>
       <c r="G62">
         <v>34.7</v>
@@ -6371,37 +6371,37 @@
         <v>53.8</v>
       </c>
       <c r="M62">
-        <v>144.267156</v>
+        <v>146.6716086</v>
       </c>
       <c r="N62">
-        <v>-90.46715600000003</v>
+        <v>-92.87160860000002</v>
       </c>
       <c r="O62">
-        <v>-14.47474496000001</v>
+        <v>-14.859457376</v>
       </c>
       <c r="P62">
-        <v>-75.99241104000002</v>
+        <v>-78.01215122400001</v>
       </c>
       <c r="Q62">
-        <v>-24.29241104000002</v>
+        <v>-26.312151224</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1900990620057908</v>
+        <v>0.1937990379546572</v>
       </c>
       <c r="T62">
-        <v>1.986330903395663</v>
+        <v>2.037262465021193</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05966708042681591</v>
+        <v>0.05868893156735992</v>
       </c>
       <c r="W62">
-        <v>0.2217305024353568</v>
+        <v>0.2219611499364166</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3729192526675994</v>
+        <v>0.3668058222959995</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2109779262635304</v>
+        <v>0.2128779262635304</v>
       </c>
       <c r="C63">
-        <v>-216.1280322039478</v>
+        <v>-230.546170534933</v>
       </c>
       <c r="D63">
-        <v>371.1889677960523</v>
+        <v>366.9678294650671</v>
       </c>
       <c r="E63">
-        <v>243.417</v>
+        <v>253.614</v>
       </c>
       <c r="F63">
-        <v>622.0170000000001</v>
+        <v>632.2140000000001</v>
       </c>
       <c r="G63">
         <v>34.7</v>
@@ -6453,37 +6453,37 @@
         <v>53.8</v>
       </c>
       <c r="M63">
-        <v>146.6716086</v>
+        <v>149.0760612</v>
       </c>
       <c r="N63">
-        <v>-92.87160860000002</v>
+        <v>-95.27606120000003</v>
       </c>
       <c r="O63">
-        <v>-14.859457376</v>
+        <v>-15.244169792</v>
       </c>
       <c r="P63">
-        <v>-78.01215122400001</v>
+        <v>-80.03189140800002</v>
       </c>
       <c r="Q63">
-        <v>-26.312151224</v>
+        <v>-28.33189140800002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1937990379546572</v>
+        <v>0.1976937494797797</v>
       </c>
       <c r="T63">
-        <v>2.037262465021193</v>
+        <v>2.090874635153329</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05868893156735992</v>
+        <v>0.05774233589691863</v>
       </c>
       <c r="W63">
-        <v>0.2219611499364166</v>
+        <v>0.2221843571955066</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3668058222959995</v>
+        <v>0.3608895993557414</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2128779262635304</v>
+        <v>0.2147779262635304</v>
       </c>
       <c r="C64">
-        <v>-230.546170534933</v>
+        <v>-244.869383297754</v>
       </c>
       <c r="D64">
-        <v>366.9678294650671</v>
+        <v>362.8416167022461</v>
       </c>
       <c r="E64">
-        <v>253.614</v>
+        <v>263.811</v>
       </c>
       <c r="F64">
-        <v>632.2140000000001</v>
+        <v>642.4110000000001</v>
       </c>
       <c r="G64">
         <v>34.7</v>
@@ -6535,37 +6535,37 @@
         <v>53.8</v>
       </c>
       <c r="M64">
-        <v>149.0760612</v>
+        <v>151.4805138</v>
       </c>
       <c r="N64">
-        <v>-95.27606120000003</v>
+        <v>-97.68051380000001</v>
       </c>
       <c r="O64">
-        <v>-15.244169792</v>
+        <v>-15.628882208</v>
       </c>
       <c r="P64">
-        <v>-80.03189140800002</v>
+        <v>-82.05163159200001</v>
       </c>
       <c r="Q64">
-        <v>-28.33189140800002</v>
+        <v>-30.351631592</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1976937494797797</v>
+        <v>0.2017989859522062</v>
       </c>
       <c r="T64">
-        <v>2.090874635153329</v>
+        <v>2.147384760427744</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05774233589691863</v>
+        <v>0.05682579088268182</v>
       </c>
       <c r="W64">
-        <v>0.2221843571955066</v>
+        <v>0.2224004785098636</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3608895993557414</v>
+        <v>0.3551611930167614</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2147779262635304</v>
+        <v>0.2166779262635304</v>
       </c>
       <c r="C65">
-        <v>-244.869383297754</v>
+        <v>-259.100836938484</v>
       </c>
       <c r="D65">
-        <v>362.8416167022461</v>
+        <v>358.8071630615161</v>
       </c>
       <c r="E65">
-        <v>263.811</v>
+        <v>274.008</v>
       </c>
       <c r="F65">
-        <v>642.4110000000001</v>
+        <v>652.6080000000001</v>
       </c>
       <c r="G65">
         <v>34.7</v>
@@ -6617,37 +6617,37 @@
         <v>53.8</v>
       </c>
       <c r="M65">
-        <v>151.4805138</v>
+        <v>153.8849664</v>
       </c>
       <c r="N65">
-        <v>-97.68051380000001</v>
+        <v>-100.0849664</v>
       </c>
       <c r="O65">
-        <v>-15.628882208</v>
+        <v>-16.013594624</v>
       </c>
       <c r="P65">
-        <v>-82.05163159200001</v>
+        <v>-84.07137177600002</v>
       </c>
       <c r="Q65">
-        <v>-30.351631592</v>
+        <v>-32.37137177600002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2017989859522062</v>
+        <v>0.2061322911175453</v>
       </c>
       <c r="T65">
-        <v>2.147384760427744</v>
+        <v>2.207034337106292</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05682579088268182</v>
+        <v>0.05593788790013992</v>
       </c>
       <c r="W65">
-        <v>0.2224004785098636</v>
+        <v>0.222609846033147</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3551611930167614</v>
+        <v>0.3496117993758745</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2166779262635304</v>
+        <v>0.2185779262635304</v>
       </c>
       <c r="C66">
-        <v>-259.100836938484</v>
+        <v>-273.2435586204136</v>
       </c>
       <c r="D66">
-        <v>358.8071630615161</v>
+        <v>354.8614413795864</v>
       </c>
       <c r="E66">
-        <v>274.008</v>
+        <v>284.205</v>
       </c>
       <c r="F66">
-        <v>652.6080000000001</v>
+        <v>662.8050000000001</v>
       </c>
       <c r="G66">
         <v>34.7</v>
@@ -6699,37 +6699,37 @@
         <v>53.8</v>
       </c>
       <c r="M66">
-        <v>153.8849664</v>
+        <v>156.289419</v>
       </c>
       <c r="N66">
-        <v>-100.0849664</v>
+        <v>-102.489419</v>
       </c>
       <c r="O66">
-        <v>-16.013594624</v>
+        <v>-16.39830704</v>
       </c>
       <c r="P66">
-        <v>-84.07137177600002</v>
+        <v>-86.09111196000001</v>
       </c>
       <c r="Q66">
-        <v>-32.37137177600002</v>
+        <v>-34.39111196</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2061322911175453</v>
+        <v>0.2107132137209038</v>
       </c>
       <c r="T66">
-        <v>2.207034337106292</v>
+        <v>2.270092461023615</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05593788790013992</v>
+        <v>0.05507730500936854</v>
       </c>
       <c r="W66">
-        <v>0.222609846033147</v>
+        <v>0.2228127714787909</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3496117993758745</v>
+        <v>0.3442331563085533</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2185779262635304</v>
+        <v>0.2204779262635304</v>
       </c>
       <c r="C67">
-        <v>-273.2435586204136</v>
+        <v>-287.3004437990597</v>
       </c>
       <c r="D67">
-        <v>354.8614413795864</v>
+        <v>351.0015562009404</v>
       </c>
       <c r="E67">
-        <v>284.205</v>
+        <v>294.402</v>
       </c>
       <c r="F67">
-        <v>662.8050000000001</v>
+        <v>673.0020000000001</v>
       </c>
       <c r="G67">
         <v>34.7</v>
@@ -6781,37 +6781,37 @@
         <v>53.8</v>
       </c>
       <c r="M67">
-        <v>156.289419</v>
+        <v>158.6938716</v>
       </c>
       <c r="N67">
-        <v>-102.489419</v>
+        <v>-104.8938716</v>
       </c>
       <c r="O67">
-        <v>-16.39830704</v>
+        <v>-16.78301945600001</v>
       </c>
       <c r="P67">
-        <v>-86.09111196000001</v>
+        <v>-88.11085214400002</v>
       </c>
       <c r="Q67">
-        <v>-34.39111196</v>
+        <v>-36.41085214400002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2107132137209038</v>
+        <v>0.2155636023597538</v>
       </c>
       <c r="T67">
-        <v>2.270092461023615</v>
+        <v>2.336859886347839</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05507730500936854</v>
+        <v>0.05424280038801447</v>
       </c>
       <c r="W67">
-        <v>0.2228127714787909</v>
+        <v>0.2230095476685062</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3442331563085533</v>
+        <v>0.3390175024250904</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2204779262635304</v>
+        <v>0.2223779262635304</v>
       </c>
       <c r="C68">
-        <v>-287.3004437990597</v>
+        <v>-301.2742633081214</v>
       </c>
       <c r="D68">
-        <v>351.0015562009404</v>
+        <v>347.2247366918787</v>
       </c>
       <c r="E68">
-        <v>294.402</v>
+        <v>304.599</v>
       </c>
       <c r="F68">
-        <v>673.0020000000001</v>
+        <v>683.1990000000001</v>
       </c>
       <c r="G68">
         <v>34.7</v>
@@ -6863,37 +6863,37 @@
         <v>53.8</v>
       </c>
       <c r="M68">
-        <v>158.6938716</v>
+        <v>161.0983242</v>
       </c>
       <c r="N68">
-        <v>-104.8938716</v>
+        <v>-107.2983242</v>
       </c>
       <c r="O68">
-        <v>-16.78301945600001</v>
+        <v>-17.16773187200001</v>
       </c>
       <c r="P68">
-        <v>-88.11085214400002</v>
+        <v>-90.13059232800003</v>
       </c>
       <c r="Q68">
-        <v>-36.41085214400002</v>
+        <v>-38.43059232800003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2155636023597538</v>
+        <v>0.220707953946413</v>
       </c>
       <c r="T68">
-        <v>2.336859886347839</v>
+        <v>2.407673822297773</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05424280038801447</v>
+        <v>0.05343320635237246</v>
       </c>
       <c r="W68">
-        <v>0.2230095476685062</v>
+        <v>0.2232004499421106</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3390175024250904</v>
+        <v>0.3339575397023279</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2223779262635304</v>
+        <v>0.2242779262635304</v>
       </c>
       <c r="C69">
-        <v>-301.2742633081214</v>
+        <v>-315.1676699928364</v>
       </c>
       <c r="D69">
-        <v>347.2247366918787</v>
+        <v>343.5283300071637</v>
       </c>
       <c r="E69">
-        <v>304.599</v>
+        <v>314.796</v>
       </c>
       <c r="F69">
-        <v>683.1990000000001</v>
+        <v>693.3960000000001</v>
       </c>
       <c r="G69">
         <v>34.7</v>
@@ -6945,37 +6945,37 @@
         <v>53.8</v>
       </c>
       <c r="M69">
-        <v>161.0983242</v>
+        <v>163.5027768</v>
       </c>
       <c r="N69">
-        <v>-107.2983242</v>
+        <v>-109.7027768</v>
       </c>
       <c r="O69">
-        <v>-17.16773187200001</v>
+        <v>-17.552444288</v>
       </c>
       <c r="P69">
-        <v>-90.13059232800003</v>
+        <v>-92.15033251200002</v>
       </c>
       <c r="Q69">
-        <v>-38.43059232800003</v>
+        <v>-40.45033251200002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.220707953946413</v>
+        <v>0.2261738275072385</v>
       </c>
       <c r="T69">
-        <v>2.407673822297773</v>
+        <v>2.482913629244579</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05343320635237246</v>
+        <v>0.05264742390601405</v>
       </c>
       <c r="W69">
-        <v>0.2232004499421106</v>
+        <v>0.2233857374429619</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3339575397023279</v>
+        <v>0.3290463994125877</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2242779262635304</v>
+        <v>0.2261779262635304</v>
       </c>
       <c r="C70">
-        <v>-315.1676699928364</v>
+        <v>-328.9832049241008</v>
       </c>
       <c r="D70">
-        <v>343.5283300071637</v>
+        <v>339.9097950758992</v>
       </c>
       <c r="E70">
-        <v>314.796</v>
+        <v>324.9930000000001</v>
       </c>
       <c r="F70">
-        <v>693.3960000000001</v>
+        <v>703.5930000000001</v>
       </c>
       <c r="G70">
         <v>34.7</v>
@@ -7027,37 +7027,37 @@
         <v>53.8</v>
       </c>
       <c r="M70">
-        <v>163.5027768</v>
+        <v>165.9072294</v>
       </c>
       <c r="N70">
-        <v>-109.7027768</v>
+        <v>-112.1072294</v>
       </c>
       <c r="O70">
-        <v>-17.552444288</v>
+        <v>-17.93715670400001</v>
       </c>
       <c r="P70">
-        <v>-92.15033251200002</v>
+        <v>-94.17007269600003</v>
       </c>
       <c r="Q70">
-        <v>-40.45033251200002</v>
+        <v>-42.47007269600003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2261738275072385</v>
+        <v>0.2319923380719881</v>
       </c>
       <c r="T70">
-        <v>2.482913629244579</v>
+        <v>2.563007617284727</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05264742390601405</v>
+        <v>0.05188441776244862</v>
       </c>
       <c r="W70">
-        <v>0.2233857374429619</v>
+        <v>0.2235656542916146</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3290463994125877</v>
+        <v>0.3242776110153038</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2261779262635304</v>
+        <v>0.2280779262635304</v>
       </c>
       <c r="C71">
-        <v>-328.9832049241008</v>
+        <v>-342.7233032239492</v>
       </c>
       <c r="D71">
-        <v>339.9097950758992</v>
+        <v>336.3666967760508</v>
       </c>
       <c r="E71">
-        <v>324.9930000000001</v>
+        <v>335.1900000000001</v>
       </c>
       <c r="F71">
-        <v>703.5930000000001</v>
+        <v>713.7900000000001</v>
       </c>
       <c r="G71">
         <v>34.7</v>
@@ -7109,37 +7109,37 @@
         <v>53.8</v>
       </c>
       <c r="M71">
-        <v>165.9072294</v>
+        <v>168.311682</v>
       </c>
       <c r="N71">
-        <v>-112.1072294</v>
+        <v>-114.511682</v>
       </c>
       <c r="O71">
-        <v>-17.93715670400001</v>
+        <v>-18.32186912</v>
       </c>
       <c r="P71">
-        <v>-94.17007269600003</v>
+        <v>-96.18981288000002</v>
       </c>
       <c r="Q71">
-        <v>-42.47007269600003</v>
+        <v>-44.48981288000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2319923380719881</v>
+        <v>0.2381987493410544</v>
       </c>
       <c r="T71">
-        <v>2.563007617284727</v>
+        <v>2.648441204527551</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05188441776244862</v>
+        <v>0.05114321179441365</v>
       </c>
       <c r="W71">
-        <v>0.2235656542916146</v>
+        <v>0.2237404306588773</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3242776110153038</v>
+        <v>0.3196450737150853</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2280779262635304</v>
+        <v>0.2299779262635304</v>
       </c>
       <c r="C72">
-        <v>-342.7233032239492</v>
+        <v>-356.3902995304558</v>
       </c>
       <c r="D72">
-        <v>336.3666967760508</v>
+        <v>332.8967004695443</v>
       </c>
       <c r="E72">
-        <v>335.1900000000001</v>
+        <v>345.3870000000001</v>
       </c>
       <c r="F72">
-        <v>713.7900000000001</v>
+        <v>723.9870000000001</v>
       </c>
       <c r="G72">
         <v>34.7</v>
@@ -7191,37 +7191,37 @@
         <v>53.8</v>
       </c>
       <c r="M72">
-        <v>168.311682</v>
+        <v>170.7161346</v>
       </c>
       <c r="N72">
-        <v>-114.511682</v>
+        <v>-116.9161346</v>
       </c>
       <c r="O72">
-        <v>-18.32186912</v>
+        <v>-18.70658153600001</v>
       </c>
       <c r="P72">
-        <v>-96.18981288000002</v>
+        <v>-98.20955306400003</v>
       </c>
       <c r="Q72">
-        <v>-44.48981288000002</v>
+        <v>-46.50955306400003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2381987493410544</v>
+        <v>0.2448331889735046</v>
       </c>
       <c r="T72">
-        <v>2.648441204527551</v>
+        <v>2.739766763304364</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05114321179441365</v>
+        <v>0.05042288486773176</v>
       </c>
       <c r="W72">
-        <v>0.2237404306588773</v>
+        <v>0.2239102837481889</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3196450737150853</v>
+        <v>0.3151430304233235</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2299779262635304</v>
+        <v>0.2318779262635304</v>
       </c>
       <c r="C73">
-        <v>-356.3902995304557</v>
+        <v>-369.9864331278301</v>
       </c>
       <c r="D73">
-        <v>332.8967004695443</v>
+        <v>329.4975668721698</v>
       </c>
       <c r="E73">
-        <v>345.3869999999999</v>
+        <v>355.5839999999999</v>
       </c>
       <c r="F73">
-        <v>723.987</v>
+        <v>734.184</v>
       </c>
       <c r="G73">
         <v>34.7</v>
@@ -7273,37 +7273,37 @@
         <v>53.8</v>
       </c>
       <c r="M73">
-        <v>170.7161346</v>
+        <v>173.1205872</v>
       </c>
       <c r="N73">
-        <v>-116.9161346</v>
+        <v>-119.3205872</v>
       </c>
       <c r="O73">
-        <v>-18.706581536</v>
+        <v>-19.091293952</v>
       </c>
       <c r="P73">
-        <v>-98.209553064</v>
+        <v>-100.229293248</v>
       </c>
       <c r="Q73">
-        <v>-46.509553064</v>
+        <v>-48.52929324799999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2448331889735045</v>
+        <v>0.2519415171511296</v>
       </c>
       <c r="T73">
-        <v>2.739766763304363</v>
+        <v>2.837615576279518</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05042288486773177</v>
+        <v>0.04972256702234661</v>
       </c>
       <c r="W73">
-        <v>0.2239102837481889</v>
+        <v>0.2240754186961307</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3151430304233236</v>
+        <v>0.3107660438896663</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2318779262635304</v>
+        <v>0.2337779262635304</v>
       </c>
       <c r="C74">
-        <v>-369.9864331278301</v>
+        <v>-383.5138527653968</v>
       </c>
       <c r="D74">
-        <v>329.4975668721698</v>
+        <v>326.1671472346031</v>
       </c>
       <c r="E74">
-        <v>355.5839999999999</v>
+        <v>365.7809999999999</v>
       </c>
       <c r="F74">
-        <v>734.184</v>
+        <v>744.381</v>
       </c>
       <c r="G74">
         <v>34.7</v>
@@ -7355,37 +7355,37 @@
         <v>53.8</v>
       </c>
       <c r="M74">
-        <v>173.1205872</v>
+        <v>175.5250398</v>
       </c>
       <c r="N74">
-        <v>-119.3205872</v>
+        <v>-121.7250398</v>
       </c>
       <c r="O74">
-        <v>-19.091293952</v>
+        <v>-19.476006368</v>
       </c>
       <c r="P74">
-        <v>-100.229293248</v>
+        <v>-102.249033432</v>
       </c>
       <c r="Q74">
-        <v>-48.52929324799999</v>
+        <v>-50.549033432</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2519415171511296</v>
+        <v>0.259576388156727</v>
       </c>
       <c r="T74">
-        <v>2.837615576279518</v>
+        <v>2.942712449475056</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04972256702234661</v>
+        <v>0.04904143596724597</v>
       </c>
       <c r="W74">
-        <v>0.2240754186961307</v>
+        <v>0.2242360293989234</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3107660438896663</v>
+        <v>0.3065089747952873</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2337779262635304</v>
+        <v>0.2356779262635304</v>
       </c>
       <c r="C75">
-        <v>-383.5138527653968</v>
+        <v>-396.9746211872493</v>
       </c>
       <c r="D75">
-        <v>326.1671472346031</v>
+        <v>322.9033788127507</v>
       </c>
       <c r="E75">
-        <v>365.7809999999999</v>
+        <v>375.978</v>
       </c>
       <c r="F75">
-        <v>744.381</v>
+        <v>754.578</v>
       </c>
       <c r="G75">
         <v>34.7</v>
@@ -7437,37 +7437,37 @@
         <v>53.8</v>
       </c>
       <c r="M75">
-        <v>175.5250398</v>
+        <v>177.9294924</v>
       </c>
       <c r="N75">
-        <v>-121.7250398</v>
+        <v>-124.1294924</v>
       </c>
       <c r="O75">
-        <v>-19.476006368</v>
+        <v>-19.860718784</v>
       </c>
       <c r="P75">
-        <v>-102.249033432</v>
+        <v>-104.268773616</v>
       </c>
       <c r="Q75">
-        <v>-50.549033432</v>
+        <v>-52.56877361600002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.259576388156727</v>
+        <v>0.2677985569319857</v>
       </c>
       <c r="T75">
-        <v>2.942712449475056</v>
+        <v>3.055893697531789</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04904143596724597</v>
+        <v>0.04837871385958048</v>
       </c>
       <c r="W75">
-        <v>0.2242360293989234</v>
+        <v>0.2243922992719109</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3065089747952873</v>
+        <v>0.302366961622378</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2356779262635304</v>
+        <v>0.2375779262635304</v>
       </c>
       <c r="C76">
-        <v>-396.9746211872493</v>
+        <v>-410.3707193926455</v>
       </c>
       <c r="D76">
-        <v>322.9033788127507</v>
+        <v>319.7042806073546</v>
       </c>
       <c r="E76">
-        <v>375.978</v>
+        <v>386.1750000000001</v>
       </c>
       <c r="F76">
-        <v>754.578</v>
+        <v>764.7750000000001</v>
       </c>
       <c r="G76">
         <v>34.7</v>
@@ -7519,37 +7519,37 @@
         <v>53.8</v>
       </c>
       <c r="M76">
-        <v>177.9294924</v>
+        <v>180.333945</v>
       </c>
       <c r="N76">
-        <v>-124.1294924</v>
+        <v>-126.533945</v>
       </c>
       <c r="O76">
-        <v>-19.860718784</v>
+        <v>-20.24543120000001</v>
       </c>
       <c r="P76">
-        <v>-104.268773616</v>
+        <v>-106.2885138</v>
       </c>
       <c r="Q76">
-        <v>-52.56877361600002</v>
+        <v>-54.58851380000003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2677985569319857</v>
+        <v>0.2766784992092652</v>
       </c>
       <c r="T76">
-        <v>3.055893697531789</v>
+        <v>3.178129445433061</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04837871385958048</v>
+        <v>0.04773366434145273</v>
       </c>
       <c r="W76">
-        <v>0.2243922992719109</v>
+        <v>0.2245444019482855</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.302366961622378</v>
+        <v>0.2983354021340796</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2375779262635304</v>
+        <v>0.2394779262635304</v>
       </c>
       <c r="C77">
-        <v>-410.3707193926455</v>
+        <v>-423.7040506456322</v>
       </c>
       <c r="D77">
-        <v>319.7042806073546</v>
+        <v>316.567949354368</v>
       </c>
       <c r="E77">
-        <v>386.1750000000001</v>
+        <v>396.3720000000001</v>
       </c>
       <c r="F77">
-        <v>764.7750000000001</v>
+        <v>774.9720000000001</v>
       </c>
       <c r="G77">
         <v>34.7</v>
@@ -7601,37 +7601,37 @@
         <v>53.8</v>
       </c>
       <c r="M77">
-        <v>180.333945</v>
+        <v>182.7383976</v>
       </c>
       <c r="N77">
-        <v>-126.533945</v>
+        <v>-128.9383976</v>
       </c>
       <c r="O77">
-        <v>-20.24543120000001</v>
+        <v>-20.63014361600001</v>
       </c>
       <c r="P77">
-        <v>-106.2885138</v>
+        <v>-108.308253984</v>
       </c>
       <c r="Q77">
-        <v>-54.58851380000003</v>
+        <v>-56.60825398400003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2766784992092652</v>
+        <v>0.2862984366763179</v>
       </c>
       <c r="T77">
-        <v>3.178129445433061</v>
+        <v>3.310551505659438</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04773366434145273</v>
+        <v>0.04710558981064415</v>
       </c>
       <c r="W77">
-        <v>0.2245444019482855</v>
+        <v>0.2246925019226501</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2983354021340796</v>
+        <v>0.2944099363165259</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2394779262635304</v>
+        <v>0.2413779262635304</v>
       </c>
       <c r="C78">
-        <v>-423.7040506456322</v>
+        <v>-436.9764442509558</v>
       </c>
       <c r="D78">
-        <v>316.567949354368</v>
+        <v>313.4925557490444</v>
       </c>
       <c r="E78">
-        <v>396.3720000000001</v>
+        <v>406.5690000000001</v>
       </c>
       <c r="F78">
-        <v>774.9720000000001</v>
+        <v>785.1690000000001</v>
       </c>
       <c r="G78">
         <v>34.7</v>
@@ -7683,37 +7683,37 @@
         <v>53.8</v>
       </c>
       <c r="M78">
-        <v>182.7383976</v>
+        <v>185.1428502</v>
       </c>
       <c r="N78">
-        <v>-128.9383976</v>
+        <v>-131.3428502</v>
       </c>
       <c r="O78">
-        <v>-20.63014361600001</v>
+        <v>-21.01485603200001</v>
       </c>
       <c r="P78">
-        <v>-108.308253984</v>
+        <v>-110.327994168</v>
       </c>
       <c r="Q78">
-        <v>-56.60825398400003</v>
+        <v>-58.62799416800003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2862984366763179</v>
+        <v>0.2967548904448535</v>
       </c>
       <c r="T78">
-        <v>3.310551505659438</v>
+        <v>3.454488527644631</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04710558981064415</v>
+        <v>0.0464938289040124</v>
       </c>
       <c r="W78">
-        <v>0.2246925019226501</v>
+        <v>0.2248367551444339</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2944099363165259</v>
+        <v>0.2905864306500774</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2413779262635304</v>
+        <v>0.2432779262635305</v>
       </c>
       <c r="C79">
-        <v>-436.9764442509558</v>
+        <v>-450.1896591119946</v>
       </c>
       <c r="D79">
-        <v>313.4925557490444</v>
+        <v>310.4763408880055</v>
       </c>
       <c r="E79">
-        <v>406.5690000000001</v>
+        <v>416.7660000000001</v>
       </c>
       <c r="F79">
-        <v>785.1690000000001</v>
+        <v>795.3660000000001</v>
       </c>
       <c r="G79">
         <v>34.7</v>
@@ -7765,37 +7765,37 @@
         <v>53.8</v>
       </c>
       <c r="M79">
-        <v>185.1428502</v>
+        <v>187.5473028</v>
       </c>
       <c r="N79">
-        <v>-131.3428502</v>
+        <v>-133.7473028000001</v>
       </c>
       <c r="O79">
-        <v>-21.01485603200001</v>
+        <v>-21.39956844800001</v>
       </c>
       <c r="P79">
-        <v>-110.327994168</v>
+        <v>-112.347734352</v>
       </c>
       <c r="Q79">
-        <v>-58.62799416800003</v>
+        <v>-60.64773435200004</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2967548904448535</v>
+        <v>0.3081619309196196</v>
       </c>
       <c r="T79">
-        <v>3.454488527644631</v>
+        <v>3.611510733446661</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0464938289040124</v>
+        <v>0.04589775417447377</v>
       </c>
       <c r="W79">
-        <v>0.2248367551444339</v>
+        <v>0.2249773095656591</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2905864306500774</v>
+        <v>0.2868609635904611</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2432779262635305</v>
+        <v>0.2451779262635304</v>
       </c>
       <c r="C80">
-        <v>-450.1896591119946</v>
+        <v>-463.3453870852583</v>
       </c>
       <c r="D80">
-        <v>310.4763408880055</v>
+        <v>307.5176129147418</v>
       </c>
       <c r="E80">
-        <v>416.7660000000001</v>
+        <v>426.9630000000001</v>
       </c>
       <c r="F80">
-        <v>795.3660000000001</v>
+        <v>805.5630000000001</v>
       </c>
       <c r="G80">
         <v>34.7</v>
@@ -7847,37 +7847,37 @@
         <v>53.8</v>
       </c>
       <c r="M80">
-        <v>187.5473028</v>
+        <v>189.9517554</v>
       </c>
       <c r="N80">
-        <v>-133.7473028000001</v>
+        <v>-136.1517554</v>
       </c>
       <c r="O80">
-        <v>-21.39956844800001</v>
+        <v>-21.784280864</v>
       </c>
       <c r="P80">
-        <v>-112.347734352</v>
+        <v>-114.367474536</v>
       </c>
       <c r="Q80">
-        <v>-60.64773435200004</v>
+        <v>-62.667474536</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3081619309196196</v>
+        <v>0.3206553562015062</v>
       </c>
       <c r="T80">
-        <v>3.611510733446661</v>
+        <v>3.783487435039358</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04589775417447377</v>
+        <v>0.04531676994441715</v>
       </c>
       <c r="W80">
-        <v>0.2249773095656591</v>
+        <v>0.2251143056471064</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2868609635904611</v>
+        <v>0.2832298121526072</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2451779262635304</v>
+        <v>0.2470779262635304</v>
       </c>
       <c r="C81">
-        <v>-463.3453870852583</v>
+        <v>-476.4452561448938</v>
       </c>
       <c r="D81">
-        <v>307.5176129147418</v>
+        <v>304.6147438551063</v>
       </c>
       <c r="E81">
-        <v>426.9630000000001</v>
+        <v>437.1600000000001</v>
       </c>
       <c r="F81">
-        <v>805.5630000000001</v>
+        <v>815.7600000000001</v>
       </c>
       <c r="G81">
         <v>34.7</v>
@@ -7929,37 +7929,37 @@
         <v>53.8</v>
       </c>
       <c r="M81">
-        <v>189.9517554</v>
+        <v>192.356208</v>
       </c>
       <c r="N81">
-        <v>-136.1517554</v>
+        <v>-138.556208</v>
       </c>
       <c r="O81">
-        <v>-21.784280864</v>
+        <v>-22.16899328000001</v>
       </c>
       <c r="P81">
-        <v>-114.367474536</v>
+        <v>-116.38721472</v>
       </c>
       <c r="Q81">
-        <v>-62.667474536</v>
+        <v>-64.68721472000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3206553562015062</v>
+        <v>0.3343981240115816</v>
       </c>
       <c r="T81">
-        <v>3.783487435039358</v>
+        <v>3.972661806791327</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04531676994441715</v>
+        <v>0.04475031032011193</v>
       </c>
       <c r="W81">
-        <v>0.2251143056471064</v>
+        <v>0.2252478768265176</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2832298121526072</v>
+        <v>0.2796894395006997</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2470779262635304</v>
+        <v>0.2489779262635304</v>
       </c>
       <c r="C82">
-        <v>-476.4452561448938</v>
+        <v>-489.4908333696363</v>
       </c>
       <c r="D82">
-        <v>304.6147438551063</v>
+        <v>301.7661666303638</v>
       </c>
       <c r="E82">
-        <v>437.1600000000001</v>
+        <v>447.3570000000001</v>
       </c>
       <c r="F82">
-        <v>815.7600000000001</v>
+        <v>825.9570000000001</v>
       </c>
       <c r="G82">
         <v>34.7</v>
@@ -8011,37 +8011,37 @@
         <v>53.8</v>
       </c>
       <c r="M82">
-        <v>192.356208</v>
+        <v>194.7606606</v>
       </c>
       <c r="N82">
-        <v>-138.556208</v>
+        <v>-140.9606606</v>
       </c>
       <c r="O82">
-        <v>-22.16899328000001</v>
+        <v>-22.55370569600001</v>
       </c>
       <c r="P82">
-        <v>-116.38721472</v>
+        <v>-118.406954904</v>
       </c>
       <c r="Q82">
-        <v>-64.68721472000001</v>
+        <v>-66.70695490400003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3343981240115816</v>
+        <v>0.3495874989595596</v>
       </c>
       <c r="T82">
-        <v>3.972661806791327</v>
+        <v>4.181749270306661</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04475031032011193</v>
+        <v>0.04419783735319698</v>
       </c>
       <c r="W82">
-        <v>0.2252478768265176</v>
+        <v>0.2253781499521162</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2796894395006997</v>
+        <v>0.276236483457481</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2489779262635304</v>
+        <v>0.2508779262635304</v>
       </c>
       <c r="C83">
-        <v>-489.4908333696363</v>
+        <v>-502.4836277637191</v>
       </c>
       <c r="D83">
-        <v>301.7661666303638</v>
+        <v>298.970372236281</v>
       </c>
       <c r="E83">
-        <v>447.3570000000001</v>
+        <v>457.5540000000001</v>
       </c>
       <c r="F83">
-        <v>825.9570000000001</v>
+        <v>836.1540000000001</v>
       </c>
       <c r="G83">
         <v>34.7</v>
@@ -8093,37 +8093,37 @@
         <v>53.8</v>
       </c>
       <c r="M83">
-        <v>194.7606606</v>
+        <v>197.1651132</v>
       </c>
       <c r="N83">
-        <v>-140.9606606</v>
+        <v>-143.3651132000001</v>
       </c>
       <c r="O83">
-        <v>-22.55370569600001</v>
+        <v>-22.93841811200001</v>
       </c>
       <c r="P83">
-        <v>-118.406954904</v>
+        <v>-120.426695088</v>
       </c>
       <c r="Q83">
-        <v>-66.70695490400003</v>
+        <v>-68.72669508800004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3495874989595596</v>
+        <v>0.3664645822350907</v>
       </c>
       <c r="T83">
-        <v>4.181749270306661</v>
+        <v>4.414068674212586</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04419783735319698</v>
+        <v>0.04365883933669457</v>
       </c>
       <c r="W83">
-        <v>0.2253781499521162</v>
+        <v>0.2255052456844074</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.276236483457481</v>
+        <v>0.272867745854341</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2508779262635304</v>
+        <v>0.2527779262635304</v>
       </c>
       <c r="C84">
-        <v>-502.4836277637191</v>
+        <v>-515.4250929224128</v>
       </c>
       <c r="D84">
-        <v>298.970372236281</v>
+        <v>296.2259070775874</v>
       </c>
       <c r="E84">
-        <v>457.5540000000001</v>
+        <v>467.7510000000001</v>
       </c>
       <c r="F84">
-        <v>836.1540000000001</v>
+        <v>846.3510000000001</v>
       </c>
       <c r="G84">
         <v>34.7</v>
@@ -8175,37 +8175,37 @@
         <v>53.8</v>
       </c>
       <c r="M84">
-        <v>197.1651132</v>
+        <v>199.5695658</v>
       </c>
       <c r="N84">
-        <v>-143.3651132000001</v>
+        <v>-145.7695658</v>
       </c>
       <c r="O84">
-        <v>-22.93841811200001</v>
+        <v>-23.323130528</v>
       </c>
       <c r="P84">
-        <v>-120.426695088</v>
+        <v>-122.446435272</v>
       </c>
       <c r="Q84">
-        <v>-68.72669508800004</v>
+        <v>-70.746435272</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3664645822350907</v>
+        <v>0.3853272047195078</v>
       </c>
       <c r="T84">
-        <v>4.414068674212586</v>
+        <v>4.673719772695679</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04365883933669457</v>
+        <v>0.04313282922420428</v>
       </c>
       <c r="W84">
-        <v>0.2255052456844074</v>
+        <v>0.2256292788689326</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.272867745854341</v>
+        <v>0.2695801826512768</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2527779262635304</v>
+        <v>0.2546779262635304</v>
       </c>
       <c r="C85">
-        <v>-515.4250929224128</v>
+        <v>-528.3166295520867</v>
       </c>
       <c r="D85">
-        <v>296.2259070775874</v>
+        <v>293.5313704479134</v>
       </c>
       <c r="E85">
-        <v>467.7510000000001</v>
+        <v>477.9480000000001</v>
       </c>
       <c r="F85">
-        <v>846.3510000000001</v>
+        <v>856.5480000000001</v>
       </c>
       <c r="G85">
         <v>34.7</v>
@@ -8257,37 +8257,37 @@
         <v>53.8</v>
       </c>
       <c r="M85">
-        <v>199.5695658</v>
+        <v>201.9740184</v>
       </c>
       <c r="N85">
-        <v>-145.7695658</v>
+        <v>-148.1740184</v>
       </c>
       <c r="O85">
-        <v>-23.323130528</v>
+        <v>-23.707842944</v>
       </c>
       <c r="P85">
-        <v>-122.446435272</v>
+        <v>-124.466175456</v>
       </c>
       <c r="Q85">
-        <v>-70.746435272</v>
+        <v>-72.76617545600001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3853272047195078</v>
+        <v>0.406547655014477</v>
       </c>
       <c r="T85">
-        <v>4.673719772695679</v>
+        <v>4.96582725848916</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04313282922420428</v>
+        <v>0.04261934316201137</v>
       </c>
       <c r="W85">
-        <v>0.2256292788689326</v>
+        <v>0.2257503588823978</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2695801826512768</v>
+        <v>0.2663708947625711</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2546779262635304</v>
+        <v>0.2565779262635304</v>
       </c>
       <c r="C86">
-        <v>-528.3166295520866</v>
+        <v>-541.1595878539713</v>
       </c>
       <c r="D86">
-        <v>293.5313704479134</v>
+        <v>290.8854121460288</v>
       </c>
       <c r="E86">
-        <v>477.948</v>
+        <v>488.145</v>
       </c>
       <c r="F86">
-        <v>856.548</v>
+        <v>866.745</v>
       </c>
       <c r="G86">
         <v>34.7</v>
@@ -8339,37 +8339,37 @@
         <v>53.8</v>
       </c>
       <c r="M86">
-        <v>201.9740184</v>
+        <v>204.378471</v>
       </c>
       <c r="N86">
-        <v>-148.1740184</v>
+        <v>-150.578471</v>
       </c>
       <c r="O86">
-        <v>-23.707842944</v>
+        <v>-24.09255536000001</v>
       </c>
       <c r="P86">
-        <v>-124.466175456</v>
+        <v>-126.48591564</v>
       </c>
       <c r="Q86">
-        <v>-72.76617545600001</v>
+        <v>-74.78591564000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4065476550144769</v>
+        <v>0.4305974986821087</v>
       </c>
       <c r="T86">
-        <v>4.965827258489157</v>
+        <v>5.296882409055101</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04261934316201137</v>
+        <v>0.04211793912481124</v>
       </c>
       <c r="W86">
-        <v>0.2257503588823978</v>
+        <v>0.2258685899543695</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.266370894762571</v>
+        <v>0.2632371195300701</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2565779262635304</v>
+        <v>0.2584779262635304</v>
       </c>
       <c r="C87">
-        <v>-541.1595878539713</v>
+        <v>-553.9552697801464</v>
       </c>
       <c r="D87">
-        <v>290.8854121460288</v>
+        <v>288.2867302198536</v>
       </c>
       <c r="E87">
-        <v>488.145</v>
+        <v>498.342</v>
       </c>
       <c r="F87">
-        <v>866.745</v>
+        <v>876.942</v>
       </c>
       <c r="G87">
         <v>34.7</v>
@@ -8421,37 +8421,37 @@
         <v>53.8</v>
       </c>
       <c r="M87">
-        <v>204.378471</v>
+        <v>206.7829236</v>
       </c>
       <c r="N87">
-        <v>-150.578471</v>
+        <v>-152.9829236</v>
       </c>
       <c r="O87">
-        <v>-24.09255536000001</v>
+        <v>-24.477267776</v>
       </c>
       <c r="P87">
-        <v>-126.48591564</v>
+        <v>-128.505655824</v>
       </c>
       <c r="Q87">
-        <v>-74.78591564000003</v>
+        <v>-76.805655824</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4305974986821087</v>
+        <v>0.4580830343022593</v>
       </c>
       <c r="T87">
-        <v>5.296882409055101</v>
+        <v>5.675231152559037</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04211793912481124</v>
+        <v>0.04162819564661576</v>
       </c>
       <c r="W87">
-        <v>0.2258685899543695</v>
+        <v>0.225984071466528</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2632371195300701</v>
+        <v>0.2601762227913486</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2584779262635304</v>
+        <v>0.2603779262635304</v>
       </c>
       <c r="C88">
-        <v>-553.9552697801464</v>
+        <v>-566.7049311696736</v>
       </c>
       <c r="D88">
-        <v>288.2867302198536</v>
+        <v>285.7340688303264</v>
       </c>
       <c r="E88">
-        <v>498.342</v>
+        <v>508.539</v>
       </c>
       <c r="F88">
-        <v>876.942</v>
+        <v>887.139</v>
       </c>
       <c r="G88">
         <v>34.7</v>
@@ -8503,37 +8503,37 @@
         <v>53.8</v>
       </c>
       <c r="M88">
-        <v>206.7829236</v>
+        <v>209.1873762</v>
       </c>
       <c r="N88">
-        <v>-152.9829236</v>
+        <v>-155.3873762</v>
       </c>
       <c r="O88">
-        <v>-24.477267776</v>
+        <v>-24.861980192</v>
       </c>
       <c r="P88">
-        <v>-128.505655824</v>
+        <v>-130.525396008</v>
       </c>
       <c r="Q88">
-        <v>-76.805655824</v>
+        <v>-78.825396008</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4580830343022593</v>
+        <v>0.4897971138639715</v>
       </c>
       <c r="T88">
-        <v>5.675231152559037</v>
+        <v>6.111787395063578</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04162819564661576</v>
+        <v>0.0411497106391834</v>
       </c>
       <c r="W88">
-        <v>0.225984071466528</v>
+        <v>0.2260968982312806</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2601762227913486</v>
+        <v>0.2571856914948962</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2603779262635304</v>
+        <v>0.2622779262635304</v>
       </c>
       <c r="C89">
-        <v>-566.7049311696736</v>
+        <v>-579.4097837722375</v>
       </c>
       <c r="D89">
-        <v>285.7340688303264</v>
+        <v>283.2262162277625</v>
       </c>
       <c r="E89">
-        <v>508.539</v>
+        <v>518.736</v>
       </c>
       <c r="F89">
-        <v>887.139</v>
+        <v>897.336</v>
       </c>
       <c r="G89">
         <v>34.7</v>
@@ -8585,37 +8585,37 @@
         <v>53.8</v>
       </c>
       <c r="M89">
-        <v>209.1873762</v>
+        <v>211.5918288</v>
       </c>
       <c r="N89">
-        <v>-155.3873762</v>
+        <v>-157.7918288</v>
       </c>
       <c r="O89">
-        <v>-24.861980192</v>
+        <v>-25.246692608</v>
       </c>
       <c r="P89">
-        <v>-130.525396008</v>
+        <v>-132.545136192</v>
       </c>
       <c r="Q89">
-        <v>-78.825396008</v>
+        <v>-80.84513619200003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4897971138639715</v>
+        <v>0.5267968733526358</v>
       </c>
       <c r="T89">
-        <v>6.111787395063578</v>
+        <v>6.621103011318876</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0411497106391834</v>
+        <v>0.04068210029101086</v>
       </c>
       <c r="W89">
-        <v>0.2260968982312806</v>
+        <v>0.2262071607513796</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2571856914948962</v>
+        <v>0.2542631268188178</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2622779262635304</v>
+        <v>0.2641779262635304</v>
       </c>
       <c r="C90">
-        <v>-579.4097837722375</v>
+        <v>-592.070997166147</v>
       </c>
       <c r="D90">
-        <v>283.2262162277625</v>
+        <v>280.7620028338531</v>
       </c>
       <c r="E90">
-        <v>518.736</v>
+        <v>528.933</v>
       </c>
       <c r="F90">
-        <v>897.336</v>
+        <v>907.533</v>
       </c>
       <c r="G90">
         <v>34.7</v>
@@ -8667,37 +8667,37 @@
         <v>53.8</v>
       </c>
       <c r="M90">
-        <v>211.5918288</v>
+        <v>213.9962814</v>
       </c>
       <c r="N90">
-        <v>-157.7918288</v>
+        <v>-160.1962814</v>
       </c>
       <c r="O90">
-        <v>-25.246692608</v>
+        <v>-25.63140502400001</v>
       </c>
       <c r="P90">
-        <v>-132.545136192</v>
+        <v>-134.564876376</v>
       </c>
       <c r="Q90">
-        <v>-80.84513619200003</v>
+        <v>-82.86487637600003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5267968733526358</v>
+        <v>0.5705238618392392</v>
       </c>
       <c r="T90">
-        <v>6.621103011318876</v>
+        <v>7.223021466893321</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04068210029101086</v>
+        <v>0.04022499804055005</v>
       </c>
       <c r="W90">
-        <v>0.2262071607513796</v>
+        <v>0.2263149454620383</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2542631268188178</v>
+        <v>0.2514062377534378</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2641779262635304</v>
+        <v>0.2660779262635304</v>
       </c>
       <c r="C91">
-        <v>-592.070997166147</v>
+        <v>-604.6897005770738</v>
       </c>
       <c r="D91">
-        <v>280.7620028338531</v>
+        <v>278.3402994229261</v>
       </c>
       <c r="E91">
-        <v>528.933</v>
+        <v>539.13</v>
       </c>
       <c r="F91">
-        <v>907.533</v>
+        <v>917.73</v>
       </c>
       <c r="G91">
         <v>34.7</v>
@@ -8749,37 +8749,37 @@
         <v>53.8</v>
       </c>
       <c r="M91">
-        <v>213.9962814</v>
+        <v>216.400734</v>
       </c>
       <c r="N91">
-        <v>-160.1962814</v>
+        <v>-162.600734</v>
       </c>
       <c r="O91">
-        <v>-25.63140502400001</v>
+        <v>-26.01611744</v>
       </c>
       <c r="P91">
-        <v>-134.564876376</v>
+        <v>-136.58461656</v>
       </c>
       <c r="Q91">
-        <v>-82.86487637600003</v>
+        <v>-84.88461656</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5705238618392392</v>
+        <v>0.622996248023163</v>
       </c>
       <c r="T91">
-        <v>7.223021466893321</v>
+        <v>7.945323613582652</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04022499804055005</v>
+        <v>0.03977805361787728</v>
       </c>
       <c r="W91">
-        <v>0.2263149454620383</v>
+        <v>0.2264203349569045</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2514062377534378</v>
+        <v>0.248612835111733</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2660779262635304</v>
+        <v>0.2679779262635304</v>
       </c>
       <c r="C92">
-        <v>-604.6897005770738</v>
+        <v>-617.266984603473</v>
       </c>
       <c r="D92">
-        <v>278.3402994229261</v>
+        <v>275.960015396527</v>
       </c>
       <c r="E92">
-        <v>539.13</v>
+        <v>549.327</v>
       </c>
       <c r="F92">
-        <v>917.73</v>
+        <v>927.927</v>
       </c>
       <c r="G92">
         <v>34.7</v>
@@ -8831,37 +8831,37 @@
         <v>53.8</v>
       </c>
       <c r="M92">
-        <v>216.400734</v>
+        <v>218.8051866</v>
       </c>
       <c r="N92">
-        <v>-162.600734</v>
+        <v>-165.0051866</v>
       </c>
       <c r="O92">
-        <v>-26.01611744</v>
+        <v>-26.400829856</v>
       </c>
       <c r="P92">
-        <v>-136.58461656</v>
+        <v>-138.604356744</v>
       </c>
       <c r="Q92">
-        <v>-84.88461656</v>
+        <v>-86.904356744</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.622996248023163</v>
+        <v>0.6871291644701812</v>
       </c>
       <c r="T92">
-        <v>7.945323613582652</v>
+        <v>8.828137348425171</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03977805361787728</v>
+        <v>0.03934093214954896</v>
       </c>
       <c r="W92">
-        <v>0.2264203349569045</v>
+        <v>0.2265234081991364</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.248612835111733</v>
+        <v>0.2458808259346811</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2679779262635304</v>
+        <v>0.2698779262635304</v>
       </c>
       <c r="C93">
-        <v>-617.266984603473</v>
+        <v>-629.8039028542194</v>
       </c>
       <c r="D93">
-        <v>275.960015396527</v>
+        <v>273.6200971457807</v>
       </c>
       <c r="E93">
-        <v>549.327</v>
+        <v>559.5240000000001</v>
       </c>
       <c r="F93">
-        <v>927.927</v>
+        <v>938.1240000000001</v>
       </c>
       <c r="G93">
         <v>34.7</v>
@@ -8913,37 +8913,37 @@
         <v>53.8</v>
       </c>
       <c r="M93">
-        <v>218.8051866</v>
+        <v>221.2096392000001</v>
       </c>
       <c r="N93">
-        <v>-165.0051866</v>
+        <v>-167.4096392000001</v>
       </c>
       <c r="O93">
-        <v>-26.400829856</v>
+        <v>-26.78554227200001</v>
       </c>
       <c r="P93">
-        <v>-138.604356744</v>
+        <v>-140.6240969280001</v>
       </c>
       <c r="Q93">
-        <v>-86.904356744</v>
+        <v>-88.92409692800005</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6871291644701812</v>
+        <v>0.767295310028954</v>
       </c>
       <c r="T93">
-        <v>8.828137348425171</v>
+        <v>9.93165451697832</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03934093214954896</v>
+        <v>0.03891331332183647</v>
       </c>
       <c r="W93">
-        <v>0.2265234081991364</v>
+        <v>0.226624240718711</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2458808259346811</v>
+        <v>0.2432082082614778</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2698779262635304</v>
+        <v>0.2717779262635304</v>
       </c>
       <c r="C94">
-        <v>-629.8039028542194</v>
+        <v>-642.301473503632</v>
       </c>
       <c r="D94">
-        <v>273.6200971457807</v>
+        <v>271.3195264963682</v>
       </c>
       <c r="E94">
-        <v>559.5240000000001</v>
+        <v>569.7210000000001</v>
       </c>
       <c r="F94">
-        <v>938.1240000000001</v>
+        <v>948.3210000000001</v>
       </c>
       <c r="G94">
         <v>34.7</v>
@@ -8995,37 +8995,37 @@
         <v>53.8</v>
       </c>
       <c r="M94">
-        <v>221.2096392000001</v>
+        <v>223.6140918</v>
       </c>
       <c r="N94">
-        <v>-167.4096392000001</v>
+        <v>-169.8140918</v>
       </c>
       <c r="O94">
-        <v>-26.78554227200001</v>
+        <v>-27.170254688</v>
       </c>
       <c r="P94">
-        <v>-140.6240969280001</v>
+        <v>-142.643837112</v>
       </c>
       <c r="Q94">
-        <v>-88.92409692800005</v>
+        <v>-90.94383711200003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.767295310028954</v>
+        <v>0.870366068604519</v>
       </c>
       <c r="T94">
-        <v>9.93165451697832</v>
+        <v>11.35046230511808</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03891331332183647</v>
+        <v>0.03849489059794575</v>
       </c>
       <c r="W94">
-        <v>0.226624240718711</v>
+        <v>0.2267229047970044</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2432082082614778</v>
+        <v>0.240593066237161</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2717779262635304</v>
+        <v>0.2736779262635304</v>
       </c>
       <c r="C95">
-        <v>-642.301473503632</v>
+        <v>-654.7606807687048</v>
       </c>
       <c r="D95">
-        <v>271.3195264963682</v>
+        <v>269.0573192312954</v>
       </c>
       <c r="E95">
-        <v>569.7210000000001</v>
+        <v>579.9180000000001</v>
       </c>
       <c r="F95">
-        <v>948.3210000000001</v>
+        <v>958.5180000000001</v>
       </c>
       <c r="G95">
         <v>34.7</v>
@@ -9077,37 +9077,37 @@
         <v>53.8</v>
       </c>
       <c r="M95">
-        <v>223.6140918</v>
+        <v>226.0185444000001</v>
       </c>
       <c r="N95">
-        <v>-169.8140918</v>
+        <v>-172.2185444</v>
       </c>
       <c r="O95">
-        <v>-27.170254688</v>
+        <v>-27.55496710400001</v>
       </c>
       <c r="P95">
-        <v>-142.643837112</v>
+        <v>-144.663577296</v>
       </c>
       <c r="Q95">
-        <v>-90.94383711200003</v>
+        <v>-92.96357729600003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.870366068604519</v>
+        <v>1.007793746705272</v>
       </c>
       <c r="T95">
-        <v>11.35046230511808</v>
+        <v>13.24220602263776</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03849489059794575</v>
+        <v>0.03808537048520165</v>
       </c>
       <c r="W95">
-        <v>0.2267229047970044</v>
+        <v>0.2268194696395895</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.240593066237161</v>
+        <v>0.2380335655325103</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2736779262635304</v>
+        <v>0.2755779262635304</v>
       </c>
       <c r="C96">
-        <v>-654.7606807687048</v>
+        <v>-667.1824763130478</v>
       </c>
       <c r="D96">
-        <v>269.0573192312954</v>
+        <v>266.8325236869524</v>
       </c>
       <c r="E96">
-        <v>579.9180000000001</v>
+        <v>590.1150000000001</v>
       </c>
       <c r="F96">
-        <v>958.5180000000001</v>
+        <v>968.7150000000001</v>
       </c>
       <c r="G96">
         <v>34.7</v>
@@ -9159,37 +9159,37 @@
         <v>53.8</v>
       </c>
       <c r="M96">
-        <v>226.0185444000001</v>
+        <v>228.422997</v>
       </c>
       <c r="N96">
-        <v>-172.2185444</v>
+        <v>-174.6229970000001</v>
       </c>
       <c r="O96">
-        <v>-27.55496710400001</v>
+        <v>-27.93967952000001</v>
       </c>
       <c r="P96">
-        <v>-144.663577296</v>
+        <v>-146.6833174800001</v>
       </c>
       <c r="Q96">
-        <v>-92.96357729600003</v>
+        <v>-94.98331748000005</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.007793746705272</v>
+        <v>1.200192496046328</v>
       </c>
       <c r="T96">
-        <v>13.24220602263776</v>
+        <v>15.89064722716533</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03808537048520165</v>
+        <v>0.03768447184851532</v>
       </c>
       <c r="W96">
-        <v>0.2268194696395895</v>
+        <v>0.2269140015381201</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2380335655325103</v>
+        <v>0.2355279490532206</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2755779262635304</v>
+        <v>0.2774779262635304</v>
       </c>
       <c r="C97">
-        <v>-667.1824763130478</v>
+        <v>-679.567780581744</v>
       </c>
       <c r="D97">
-        <v>266.8325236869524</v>
+        <v>264.6442194182561</v>
       </c>
       <c r="E97">
-        <v>590.1150000000001</v>
+        <v>600.3120000000001</v>
       </c>
       <c r="F97">
-        <v>968.7150000000001</v>
+        <v>978.9120000000001</v>
       </c>
       <c r="G97">
         <v>34.7</v>
@@ -9241,37 +9241,37 @@
         <v>53.8</v>
       </c>
       <c r="M97">
-        <v>228.422997</v>
+        <v>230.8274496000001</v>
       </c>
       <c r="N97">
-        <v>-174.6229970000001</v>
+        <v>-177.0274496000001</v>
       </c>
       <c r="O97">
-        <v>-27.93967952000001</v>
+        <v>-28.32439193600001</v>
       </c>
       <c r="P97">
-        <v>-146.6833174800001</v>
+        <v>-148.7030576640001</v>
       </c>
       <c r="Q97">
-        <v>-94.98331748000005</v>
+        <v>-97.00305766400005</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.200192496046328</v>
+        <v>1.48879062005791</v>
       </c>
       <c r="T97">
-        <v>15.89064722716533</v>
+        <v>19.86330903395667</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03768447184851532</v>
+        <v>0.03729192526675994</v>
       </c>
       <c r="W97">
-        <v>0.2269140015381201</v>
+        <v>0.227006564022098</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2355279490532206</v>
+        <v>0.2330745329172496</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2774779262635304</v>
+        <v>0.2793779262635304</v>
       </c>
       <c r="C98">
-        <v>-679.567780581744</v>
+        <v>-691.9174840710599</v>
       </c>
       <c r="D98">
-        <v>264.6442194182561</v>
+        <v>262.4915159289401</v>
       </c>
       <c r="E98">
-        <v>600.312</v>
+        <v>610.509</v>
       </c>
       <c r="F98">
-        <v>978.912</v>
+        <v>989.109</v>
       </c>
       <c r="G98">
         <v>34.7</v>
@@ -9323,37 +9323,37 @@
         <v>53.8</v>
       </c>
       <c r="M98">
-        <v>230.8274496</v>
+        <v>233.2319022</v>
       </c>
       <c r="N98">
-        <v>-177.0274496</v>
+        <v>-179.4319022</v>
       </c>
       <c r="O98">
-        <v>-28.324391936</v>
+        <v>-28.709104352</v>
       </c>
       <c r="P98">
-        <v>-148.703057664</v>
+        <v>-150.722797848</v>
       </c>
       <c r="Q98">
-        <v>-97.003057664</v>
+        <v>-99.02279784800002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.488790620057906</v>
+        <v>1.969787493410541</v>
       </c>
       <c r="T98">
-        <v>19.86330903395661</v>
+        <v>26.48441204527548</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03729192526675995</v>
+        <v>0.0369074724289583</v>
       </c>
       <c r="W98">
-        <v>0.227006564022098</v>
+        <v>0.2270972180012516</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2330745329172498</v>
+        <v>0.2306717026809894</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2793779262635304</v>
+        <v>0.2812779262635304</v>
       </c>
       <c r="C99">
-        <v>-691.9174840710599</v>
+        <v>-704.2324485366839</v>
       </c>
       <c r="D99">
-        <v>262.4915159289401</v>
+        <v>260.3735514633162</v>
       </c>
       <c r="E99">
-        <v>610.509</v>
+        <v>620.706</v>
       </c>
       <c r="F99">
-        <v>989.109</v>
+        <v>999.306</v>
       </c>
       <c r="G99">
         <v>34.7</v>
@@ -9405,37 +9405,37 @@
         <v>53.8</v>
       </c>
       <c r="M99">
-        <v>233.2319022</v>
+        <v>235.6363548</v>
       </c>
       <c r="N99">
-        <v>-179.4319022</v>
+        <v>-181.8363548</v>
       </c>
       <c r="O99">
-        <v>-28.709104352</v>
+        <v>-29.09381676800001</v>
       </c>
       <c r="P99">
-        <v>-150.722797848</v>
+        <v>-152.742538032</v>
       </c>
       <c r="Q99">
-        <v>-99.02279784800002</v>
+        <v>-101.042538032</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.969787493410541</v>
+        <v>2.931781240115812</v>
       </c>
       <c r="T99">
-        <v>26.48441204527548</v>
+        <v>39.72661806791322</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0369074724289583</v>
+        <v>0.03653086556743832</v>
       </c>
       <c r="W99">
-        <v>0.2270972180012516</v>
+        <v>0.227186021899198</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2306717026809894</v>
+        <v>0.2283179097964895</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2812779262635304</v>
+        <v>0.2831779262635304</v>
       </c>
       <c r="C100">
-        <v>-704.2324485366839</v>
+        <v>-716.5135081439412</v>
       </c>
       <c r="D100">
-        <v>260.3735514633162</v>
+        <v>258.2894918560589</v>
       </c>
       <c r="E100">
-        <v>620.706</v>
+        <v>630.903</v>
       </c>
       <c r="F100">
-        <v>999.306</v>
+        <v>1009.503</v>
       </c>
       <c r="G100">
         <v>34.7</v>
@@ -9487,37 +9487,37 @@
         <v>53.8</v>
       </c>
       <c r="M100">
-        <v>235.6363548</v>
+        <v>238.0408074</v>
       </c>
       <c r="N100">
-        <v>-181.8363548</v>
+        <v>-184.2408074</v>
       </c>
       <c r="O100">
-        <v>-29.09381676800001</v>
+        <v>-29.478529184</v>
       </c>
       <c r="P100">
-        <v>-152.742538032</v>
+        <v>-154.762278216</v>
       </c>
       <c r="Q100">
-        <v>-101.042538032</v>
+        <v>-103.062278216</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.931781240115812</v>
+        <v>5.817762480231625</v>
       </c>
       <c r="T100">
-        <v>39.72661806791322</v>
+        <v>79.45323613582646</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03653086556743832</v>
+        <v>0.03616186692534298</v>
       </c>
       <c r="W100">
-        <v>0.227186021899198</v>
+        <v>0.2272730317790042</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2283179097964895</v>
+        <v>0.2260116682833937</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2831779262635304</v>
-      </c>
-      <c r="C101">
-        <v>-716.5135081439412</v>
-      </c>
-      <c r="D101">
-        <v>258.2894918560589</v>
-      </c>
-      <c r="E101">
-        <v>630.903</v>
-      </c>
-      <c r="F101">
-        <v>1009.503</v>
-      </c>
-      <c r="G101">
-        <v>34.7</v>
-      </c>
-      <c r="H101">
-        <v>641.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>105.5</v>
-      </c>
-      <c r="K101">
-        <v>51.7</v>
-      </c>
-      <c r="L101">
-        <v>53.8</v>
-      </c>
-      <c r="M101">
-        <v>238.0408074</v>
-      </c>
-      <c r="N101">
-        <v>-184.2408074</v>
-      </c>
-      <c r="O101">
-        <v>-29.478529184</v>
-      </c>
-      <c r="P101">
-        <v>-154.762278216</v>
-      </c>
-      <c r="Q101">
-        <v>-103.062278216</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.817762480231625</v>
-      </c>
-      <c r="T101">
-        <v>79.45323613582646</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03616186692534298</v>
-      </c>
-      <c r="W101">
-        <v>0.2272730317790042</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2260116682833937</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
